--- a/Fig.3(d).xlsx
+++ b/Fig.3(d).xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Sachin\Research\Superconductivity\Nb\Mn3Pt_Nb\Raw data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Sachin\Research\Paper review\Mn3Pt_Nb\Dataset_2\New folder 2\Raw data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -363,7 +363,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H164"/>
+  <dimension ref="A1:H165"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.5703125" customWidth="1"/>
@@ -417,13 +417,13 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
-        <v>1.11676E-5</v>
+        <v>-1.11676E-5</v>
       </c>
       <c r="B7">
         <v>0</v>
       </c>
       <c r="C7" s="1">
-        <v>1.11676E-5</v>
+        <v>-1.6908400000000001E-4</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -443,7 +443,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
-        <v>5.69547E-4</v>
+        <v>1.11676E-5</v>
       </c>
       <c r="B8">
         <v>1.5625</v>
@@ -468,8 +468,8 @@
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>1.89E-3</v>
+      <c r="A9" s="1">
+        <v>1.0050799999999999E-4</v>
       </c>
       <c r="B9">
         <v>3.125</v>
@@ -494,8 +494,8 @@
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>4.1999999999999997E-3</v>
+      <c r="A10" s="1">
+        <v>3.5736299999999997E-4</v>
       </c>
       <c r="B10">
         <v>4.6875</v>
@@ -520,8 +520,8 @@
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>7.1999999999999998E-3</v>
+      <c r="A11" s="1">
+        <v>8.7107199999999997E-4</v>
       </c>
       <c r="B11">
         <v>6.25</v>
@@ -547,7 +547,7 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>9.8700000000000003E-3</v>
+        <v>2.1900000000000001E-3</v>
       </c>
       <c r="B12">
         <v>7.8125</v>
@@ -573,13 +573,13 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>1.2109999999999999E-2</v>
+        <v>8.1399999999999997E-3</v>
       </c>
       <c r="B13">
         <v>9.375</v>
       </c>
       <c r="C13" s="1">
-        <v>2.2335199999999999E-5</v>
+        <v>1.11676E-5</v>
       </c>
       <c r="D13">
         <v>9.375</v>
@@ -599,19 +599,19 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>1.4189999999999999E-2</v>
+        <v>1.405E-2</v>
       </c>
       <c r="B14">
         <v>10.9375</v>
       </c>
       <c r="C14" s="1">
-        <v>7.8173100000000005E-5</v>
+        <v>1.11676E-5</v>
       </c>
       <c r="D14">
         <v>10.9375</v>
       </c>
-      <c r="E14">
-        <v>0</v>
+      <c r="E14" s="1">
+        <v>1.11676E-5</v>
       </c>
       <c r="F14">
         <v>10.9375</v>
@@ -625,13 +625,13 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>1.6250000000000001E-2</v>
+        <v>1.6449999999999999E-2</v>
       </c>
       <c r="B15">
         <v>12.5</v>
       </c>
-      <c r="C15">
-        <v>6.0099999999999997E-3</v>
+      <c r="C15" s="1">
+        <v>1.11676E-5</v>
       </c>
       <c r="D15">
         <v>12.5</v>
@@ -651,19 +651,19 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>1.831E-2</v>
+        <v>1.8499999999999999E-2</v>
       </c>
       <c r="B16">
         <v>14.0625</v>
       </c>
-      <c r="C16">
-        <v>1.771E-2</v>
+      <c r="C16" s="1">
+        <v>1.11676E-5</v>
       </c>
       <c r="D16">
         <v>14.0625</v>
       </c>
-      <c r="E16">
-        <v>1.5E-3</v>
+      <c r="E16" s="1">
+        <v>1.11676E-5</v>
       </c>
       <c r="F16">
         <v>14.0625</v>
@@ -677,25 +677,25 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>2.0369999999999999E-2</v>
+        <v>2.0559999999999998E-2</v>
       </c>
       <c r="B17">
         <v>15.625</v>
       </c>
-      <c r="C17">
-        <v>2.0330000000000001E-2</v>
+      <c r="C17" s="1">
+        <v>1.11676E-5</v>
       </c>
       <c r="D17">
         <v>15.625</v>
       </c>
-      <c r="E17">
-        <v>1.8540000000000001E-2</v>
+      <c r="E17" s="1">
+        <v>1.11676E-5</v>
       </c>
       <c r="F17">
         <v>15.625</v>
       </c>
       <c r="G17">
-        <v>4.3600000000000002E-3</v>
+        <v>0</v>
       </c>
       <c r="H17">
         <v>15.625</v>
@@ -703,25 +703,25 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>2.2440000000000002E-2</v>
+        <v>2.2610000000000002E-2</v>
       </c>
       <c r="B18">
         <v>17.1875</v>
       </c>
-      <c r="C18">
-        <v>2.2409999999999999E-2</v>
+      <c r="C18" s="1">
+        <v>1.11676E-5</v>
       </c>
       <c r="D18">
         <v>17.1875</v>
       </c>
-      <c r="E18">
-        <v>2.2349999999999998E-2</v>
+      <c r="E18" s="1">
+        <v>1.11676E-5</v>
       </c>
       <c r="F18">
         <v>17.1875</v>
       </c>
       <c r="G18">
-        <v>2.1899999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="H18">
         <v>17.1875</v>
@@ -729,25 +729,25 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>2.4490000000000001E-2</v>
+        <v>2.4660000000000001E-2</v>
       </c>
       <c r="B19">
         <v>18.75</v>
       </c>
-      <c r="C19">
-        <v>2.4469999999999999E-2</v>
+      <c r="C19" s="1">
+        <v>1.11676E-5</v>
       </c>
       <c r="D19">
         <v>18.75</v>
       </c>
-      <c r="E19">
-        <v>2.445E-2</v>
+      <c r="E19" s="1">
+        <v>1.11676E-5</v>
       </c>
       <c r="F19">
         <v>18.75</v>
       </c>
       <c r="G19">
-        <v>2.435E-2</v>
+        <v>0</v>
       </c>
       <c r="H19">
         <v>18.75</v>
@@ -755,25 +755,25 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>2.6550000000000001E-2</v>
+        <v>2.6710000000000001E-2</v>
       </c>
       <c r="B20">
         <v>20.3125</v>
       </c>
-      <c r="C20">
-        <v>2.6519999999999998E-2</v>
+      <c r="C20" s="1">
+        <v>2.2335199999999999E-5</v>
       </c>
       <c r="D20">
         <v>20.3125</v>
       </c>
-      <c r="E20">
-        <v>2.6499999999999999E-2</v>
+      <c r="E20" s="1">
+        <v>1.11676E-5</v>
       </c>
       <c r="F20">
         <v>20.3125</v>
       </c>
       <c r="G20">
-        <v>2.64E-2</v>
+        <v>0</v>
       </c>
       <c r="H20">
         <v>20.3125</v>
@@ -781,25 +781,25 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>2.86E-2</v>
+        <v>2.877E-2</v>
       </c>
       <c r="B21">
         <v>21.875</v>
       </c>
-      <c r="C21">
-        <v>2.8580000000000001E-2</v>
+      <c r="C21" s="1">
+        <v>4.4670299999999998E-5</v>
       </c>
       <c r="D21">
         <v>21.875</v>
       </c>
-      <c r="E21">
-        <v>2.8559999999999999E-2</v>
+      <c r="E21" s="1">
+        <v>1.11676E-5</v>
       </c>
       <c r="F21">
         <v>21.875</v>
       </c>
       <c r="G21">
-        <v>2.844E-2</v>
+        <v>0</v>
       </c>
       <c r="H21">
         <v>21.875</v>
@@ -807,25 +807,25 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>3.066E-2</v>
+        <v>3.0810000000000001E-2</v>
       </c>
       <c r="B22">
         <v>23.4375</v>
       </c>
-      <c r="C22">
-        <v>3.0630000000000001E-2</v>
+      <c r="C22" s="1">
+        <v>1.1167600000000001E-4</v>
       </c>
       <c r="D22">
         <v>23.4375</v>
       </c>
-      <c r="E22">
-        <v>3.0620000000000001E-2</v>
+      <c r="E22" s="1">
+        <v>1.11676E-5</v>
       </c>
       <c r="F22">
         <v>23.4375</v>
       </c>
       <c r="G22">
-        <v>3.0499999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="H22">
         <v>23.4375</v>
@@ -833,25 +833,25 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>3.2710000000000003E-2</v>
+        <v>3.2870000000000003E-2</v>
       </c>
       <c r="B23">
         <v>25</v>
       </c>
-      <c r="C23">
-        <v>3.2689999999999997E-2</v>
+      <c r="C23" s="1">
+        <v>3.20935E-5</v>
       </c>
       <c r="D23">
         <v>25</v>
       </c>
-      <c r="E23">
-        <v>3.2669999999999998E-2</v>
+      <c r="E23" s="1">
+        <v>1.11676E-5</v>
       </c>
       <c r="F23">
         <v>25</v>
       </c>
       <c r="G23">
-        <v>3.2539999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="H23">
         <v>25</v>
@@ -859,25 +859,25 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>3.4759999999999999E-2</v>
+        <v>3.49E-2</v>
       </c>
       <c r="B24">
         <v>26.5625</v>
       </c>
       <c r="C24">
-        <v>3.474E-2</v>
+        <v>3.2599999999999997E-2</v>
       </c>
       <c r="D24">
         <v>26.5625</v>
       </c>
-      <c r="E24">
-        <v>3.4720000000000001E-2</v>
+      <c r="E24" s="1">
+        <v>1.11676E-5</v>
       </c>
       <c r="F24">
         <v>26.5625</v>
       </c>
       <c r="G24">
-        <v>3.4590000000000003E-2</v>
+        <v>0</v>
       </c>
       <c r="H24">
         <v>26.5625</v>
@@ -885,25 +885,25 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>3.6810000000000002E-2</v>
+        <v>3.6940000000000001E-2</v>
       </c>
       <c r="B25">
         <v>28.125</v>
       </c>
       <c r="C25">
-        <v>3.6799999999999999E-2</v>
+        <v>3.6920000000000001E-2</v>
       </c>
       <c r="D25">
         <v>28.125</v>
       </c>
-      <c r="E25">
-        <v>3.6769999999999997E-2</v>
+      <c r="E25" s="1">
+        <v>1.11676E-5</v>
       </c>
       <c r="F25">
         <v>28.125</v>
       </c>
       <c r="G25">
-        <v>3.6630000000000003E-2</v>
+        <v>0</v>
       </c>
       <c r="H25">
         <v>28.125</v>
@@ -911,25 +911,25 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>3.8870000000000002E-2</v>
+        <v>3.9E-2</v>
       </c>
       <c r="B26">
         <v>29.6875</v>
       </c>
       <c r="C26">
-        <v>3.8850000000000003E-2</v>
+        <v>3.8969999999999998E-2</v>
       </c>
       <c r="D26">
         <v>29.6875</v>
       </c>
-      <c r="E26">
-        <v>3.884E-2</v>
+      <c r="E26" s="1">
+        <v>1.11676E-5</v>
       </c>
       <c r="F26">
         <v>29.6875</v>
       </c>
       <c r="G26">
-        <v>3.8670000000000003E-2</v>
+        <v>0</v>
       </c>
       <c r="H26">
         <v>29.6875</v>
@@ -937,25 +937,25 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>4.0930000000000001E-2</v>
+        <v>4.104E-2</v>
       </c>
       <c r="B27">
         <v>31.25</v>
       </c>
       <c r="C27">
-        <v>4.0910000000000002E-2</v>
+        <v>4.1020000000000001E-2</v>
       </c>
       <c r="D27">
         <v>31.25</v>
       </c>
-      <c r="E27">
-        <v>4.088E-2</v>
+      <c r="E27" s="1">
+        <v>3.35028E-5</v>
       </c>
       <c r="F27">
         <v>31.25</v>
       </c>
       <c r="G27">
-        <v>4.0730000000000002E-2</v>
+        <v>0</v>
       </c>
       <c r="H27">
         <v>31.25</v>
@@ -963,25 +963,25 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>4.2970000000000001E-2</v>
+        <v>4.308E-2</v>
       </c>
       <c r="B28">
         <v>32.8125</v>
       </c>
       <c r="C28">
-        <v>4.2959999999999998E-2</v>
+        <v>4.3060000000000001E-2</v>
       </c>
       <c r="D28">
         <v>32.8125</v>
       </c>
-      <c r="E28">
-        <v>4.2939999999999999E-2</v>
+      <c r="E28" s="1">
+        <v>6.7005499999999994E-5</v>
       </c>
       <c r="F28">
         <v>32.8125</v>
       </c>
       <c r="G28">
-        <v>4.2770000000000002E-2</v>
+        <v>0</v>
       </c>
       <c r="H28">
         <v>32.8125</v>
@@ -989,25 +989,25 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>4.5030000000000001E-2</v>
+        <v>4.5150000000000003E-2</v>
       </c>
       <c r="B29">
         <v>34.375</v>
       </c>
       <c r="C29">
-        <v>4.5019999999999998E-2</v>
+        <v>4.5109999999999997E-2</v>
       </c>
       <c r="D29">
         <v>34.375</v>
       </c>
       <c r="E29">
-        <v>4.4990000000000002E-2</v>
+        <v>3.3300000000000003E-2</v>
       </c>
       <c r="F29">
         <v>34.375</v>
       </c>
       <c r="G29">
-        <v>4.48E-2</v>
+        <v>0</v>
       </c>
       <c r="H29">
         <v>34.375</v>
@@ -1015,25 +1015,25 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>4.709E-2</v>
+        <v>4.718E-2</v>
       </c>
       <c r="B30">
         <v>35.9375</v>
       </c>
       <c r="C30">
-        <v>4.7079999999999997E-2</v>
+        <v>4.7149999999999997E-2</v>
       </c>
       <c r="D30">
         <v>35.9375</v>
       </c>
       <c r="E30">
-        <v>4.7050000000000002E-2</v>
+        <v>4.7280000000000003E-2</v>
       </c>
       <c r="F30">
         <v>35.9375</v>
       </c>
       <c r="G30">
-        <v>4.6859999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="H30">
         <v>35.9375</v>
@@ -1041,25 +1041,25 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>4.9149999999999999E-2</v>
+        <v>4.9250000000000002E-2</v>
       </c>
       <c r="B31">
         <v>37.5</v>
       </c>
       <c r="C31">
-        <v>4.9140000000000003E-2</v>
+        <v>4.9200000000000001E-2</v>
       </c>
       <c r="D31">
         <v>37.5</v>
       </c>
       <c r="E31">
-        <v>4.9099999999999998E-2</v>
+        <v>4.9349999999999998E-2</v>
       </c>
       <c r="F31">
         <v>37.5</v>
       </c>
       <c r="G31">
-        <v>4.8899999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="H31">
         <v>37.5</v>
@@ -1067,25 +1067,25 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>5.1209999999999999E-2</v>
+        <v>5.1290000000000002E-2</v>
       </c>
       <c r="B32">
         <v>39.0625</v>
       </c>
       <c r="C32">
-        <v>5.1200000000000002E-2</v>
+        <v>5.126E-2</v>
       </c>
       <c r="D32">
         <v>39.0625</v>
       </c>
       <c r="E32">
-        <v>5.1180000000000003E-2</v>
+        <v>5.1400000000000001E-2</v>
       </c>
       <c r="F32">
         <v>39.0625</v>
       </c>
       <c r="G32">
-        <v>5.0970000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="H32">
         <v>39.0625</v>
@@ -1093,25 +1093,25 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>5.3269999999999998E-2</v>
+        <v>5.3350000000000002E-2</v>
       </c>
       <c r="B33">
         <v>40.625</v>
       </c>
       <c r="C33">
-        <v>5.3260000000000002E-2</v>
+        <v>5.33E-2</v>
       </c>
       <c r="D33">
         <v>40.625</v>
       </c>
       <c r="E33">
-        <v>5.3220000000000003E-2</v>
+        <v>5.3469999999999997E-2</v>
       </c>
       <c r="F33">
         <v>40.625</v>
       </c>
-      <c r="G33">
-        <v>5.3010000000000002E-2</v>
+      <c r="G33" s="1">
+        <v>9.0549000000000001E-4</v>
       </c>
       <c r="H33">
         <v>40.625</v>
@@ -1119,25 +1119,25 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>5.534E-2</v>
+        <v>5.5399999999999998E-2</v>
       </c>
       <c r="B34">
         <v>42.1875</v>
       </c>
       <c r="C34">
-        <v>5.5320000000000001E-2</v>
+        <v>5.5350000000000003E-2</v>
       </c>
       <c r="D34">
         <v>42.1875</v>
       </c>
       <c r="E34">
-        <v>5.5289999999999999E-2</v>
+        <v>5.5509999999999997E-2</v>
       </c>
       <c r="F34">
         <v>42.1875</v>
       </c>
       <c r="G34">
-        <v>5.5059999999999998E-2</v>
+        <v>5.534E-2</v>
       </c>
       <c r="H34">
         <v>42.1875</v>
@@ -1145,25 +1145,25 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>5.738E-2</v>
+        <v>5.7430000000000002E-2</v>
       </c>
       <c r="B35">
         <v>43.75</v>
       </c>
       <c r="C35">
-        <v>5.7369999999999997E-2</v>
+        <v>5.7389999999999997E-2</v>
       </c>
       <c r="D35">
         <v>43.75</v>
       </c>
       <c r="E35">
-        <v>5.7349999999999998E-2</v>
+        <v>5.756E-2</v>
       </c>
       <c r="F35">
         <v>43.75</v>
       </c>
       <c r="G35">
-        <v>5.7110000000000001E-2</v>
+        <v>5.738E-2</v>
       </c>
       <c r="H35">
         <v>43.75</v>
@@ -1171,25 +1171,25 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>5.9450000000000003E-2</v>
+        <v>5.9490000000000001E-2</v>
       </c>
       <c r="B36">
         <v>45.3125</v>
       </c>
       <c r="C36">
-        <v>5.9420000000000001E-2</v>
+        <v>5.9429999999999997E-2</v>
       </c>
       <c r="D36">
         <v>45.3125</v>
       </c>
       <c r="E36">
-        <v>5.9400000000000001E-2</v>
+        <v>5.9610000000000003E-2</v>
       </c>
       <c r="F36">
         <v>45.3125</v>
       </c>
       <c r="G36">
-        <v>5.9150000000000001E-2</v>
+        <v>5.9420000000000001E-2</v>
       </c>
       <c r="H36">
         <v>45.3125</v>
@@ -1197,25 +1197,25 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>6.1499999999999999E-2</v>
+        <v>6.1539999999999997E-2</v>
       </c>
       <c r="B37">
         <v>46.875</v>
       </c>
       <c r="C37">
-        <v>6.148E-2</v>
+        <v>6.1490000000000003E-2</v>
       </c>
       <c r="D37">
         <v>46.875</v>
       </c>
       <c r="E37">
-        <v>6.1460000000000001E-2</v>
+        <v>6.1670000000000003E-2</v>
       </c>
       <c r="F37">
         <v>46.875</v>
       </c>
       <c r="G37">
-        <v>6.1199999999999997E-2</v>
+        <v>6.148E-2</v>
       </c>
       <c r="H37">
         <v>46.875</v>
@@ -1223,7 +1223,7 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>6.3570000000000002E-2</v>
+        <v>6.3589999999999994E-2</v>
       </c>
       <c r="B38">
         <v>48.4375</v>
@@ -1235,13 +1235,13 @@
         <v>48.4375</v>
       </c>
       <c r="E38">
-        <v>6.3519999999999993E-2</v>
+        <v>6.3719999999999999E-2</v>
       </c>
       <c r="F38">
         <v>48.4375</v>
       </c>
       <c r="G38">
-        <v>6.3250000000000001E-2</v>
+        <v>6.3519999999999993E-2</v>
       </c>
       <c r="H38">
         <v>48.4375</v>
@@ -1249,25 +1249,25 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>6.5619999999999998E-2</v>
+        <v>6.5710000000000005E-2</v>
       </c>
       <c r="B39">
         <v>50</v>
       </c>
       <c r="C39">
-        <v>6.5600000000000006E-2</v>
+        <v>6.565E-2</v>
       </c>
       <c r="D39">
         <v>50</v>
       </c>
       <c r="E39">
-        <v>6.5579999999999999E-2</v>
+        <v>6.5839999999999996E-2</v>
       </c>
       <c r="F39">
         <v>50</v>
       </c>
       <c r="G39">
-        <v>6.5299999999999997E-2</v>
+        <v>6.5629999999999994E-2</v>
       </c>
       <c r="H39">
         <v>50</v>
@@ -1275,25 +1275,25 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>6.7739999999999995E-2</v>
+        <v>6.7750000000000005E-2</v>
       </c>
       <c r="B40">
         <v>51.5625</v>
       </c>
       <c r="C40">
-        <v>6.7720000000000002E-2</v>
+        <v>6.7699999999999996E-2</v>
       </c>
       <c r="D40">
         <v>51.5625</v>
       </c>
       <c r="E40">
-        <v>6.7699999999999996E-2</v>
+        <v>6.7900000000000002E-2</v>
       </c>
       <c r="F40">
         <v>51.5625</v>
       </c>
       <c r="G40">
-        <v>6.7419999999999994E-2</v>
+        <v>6.7680000000000004E-2</v>
       </c>
       <c r="H40">
         <v>51.5625</v>
@@ -1301,25 +1301,25 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>6.9800000000000001E-2</v>
+        <v>6.9809999999999997E-2</v>
       </c>
       <c r="B41">
         <v>53.125</v>
       </c>
       <c r="C41">
-        <v>6.9779999999999995E-2</v>
+        <v>6.9750000000000006E-2</v>
       </c>
       <c r="D41">
         <v>53.125</v>
       </c>
       <c r="E41">
-        <v>6.9750000000000006E-2</v>
+        <v>6.9949999999999998E-2</v>
       </c>
       <c r="F41">
         <v>53.125</v>
       </c>
       <c r="G41">
-        <v>6.9459999999999994E-2</v>
+        <v>6.973E-2</v>
       </c>
       <c r="H41">
         <v>53.125</v>
@@ -1327,25 +1327,25 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>7.1859999999999993E-2</v>
+        <v>7.1849999999999997E-2</v>
       </c>
       <c r="B42">
         <v>54.6875</v>
       </c>
       <c r="C42">
-        <v>7.1849999999999997E-2</v>
+        <v>7.1800000000000003E-2</v>
       </c>
       <c r="D42">
         <v>54.6875</v>
       </c>
       <c r="E42">
-        <v>7.1819999999999995E-2</v>
+        <v>7.2010000000000005E-2</v>
       </c>
       <c r="F42">
         <v>54.6875</v>
       </c>
       <c r="G42">
-        <v>7.152E-2</v>
+        <v>7.177E-2</v>
       </c>
       <c r="H42">
         <v>54.6875</v>
@@ -1353,25 +1353,25 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>7.392E-2</v>
+        <v>7.3910000000000003E-2</v>
       </c>
       <c r="B43">
         <v>56.25</v>
       </c>
       <c r="C43">
-        <v>7.3910000000000003E-2</v>
+        <v>7.3840000000000003E-2</v>
       </c>
       <c r="D43">
         <v>56.25</v>
       </c>
       <c r="E43">
-        <v>7.3870000000000005E-2</v>
+        <v>7.4060000000000001E-2</v>
       </c>
       <c r="F43">
         <v>56.25</v>
       </c>
       <c r="G43">
-        <v>7.3550000000000004E-2</v>
+        <v>7.3819999999999997E-2</v>
       </c>
       <c r="H43">
         <v>56.25</v>
@@ -1379,25 +1379,25 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>7.5980000000000006E-2</v>
+        <v>7.596E-2</v>
       </c>
       <c r="B44">
         <v>57.8125</v>
       </c>
       <c r="C44">
-        <v>7.596E-2</v>
+        <v>7.5889999999999999E-2</v>
       </c>
       <c r="D44">
         <v>57.8125</v>
       </c>
       <c r="E44">
-        <v>7.5939999999999994E-2</v>
+        <v>7.6119999999999993E-2</v>
       </c>
       <c r="F44">
         <v>57.8125</v>
       </c>
       <c r="G44">
-        <v>7.5579999999999994E-2</v>
+        <v>7.5859999999999997E-2</v>
       </c>
       <c r="H44">
         <v>57.8125</v>
@@ -1405,25 +1405,25 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>7.8039999999999998E-2</v>
+        <v>7.8020000000000006E-2</v>
       </c>
       <c r="B45">
         <v>59.375</v>
       </c>
       <c r="C45">
-        <v>7.8020000000000006E-2</v>
+        <v>7.7950000000000005E-2</v>
       </c>
       <c r="D45">
         <v>59.375</v>
       </c>
       <c r="E45">
-        <v>7.7990000000000004E-2</v>
+        <v>7.8179999999999999E-2</v>
       </c>
       <c r="F45">
         <v>59.375</v>
       </c>
       <c r="G45">
-        <v>7.7630000000000005E-2</v>
+        <v>7.7920000000000003E-2</v>
       </c>
       <c r="H45">
         <v>59.375</v>
@@ -1431,25 +1431,25 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>8.0110000000000001E-2</v>
+        <v>8.0070000000000002E-2</v>
       </c>
       <c r="B46">
         <v>60.9375</v>
       </c>
       <c r="C46">
-        <v>8.0079999999999998E-2</v>
+        <v>0.08</v>
       </c>
       <c r="D46">
         <v>60.9375</v>
       </c>
       <c r="E46">
-        <v>8.0060000000000006E-2</v>
+        <v>8.0240000000000006E-2</v>
       </c>
       <c r="F46">
         <v>60.9375</v>
       </c>
       <c r="G46">
-        <v>7.9689999999999997E-2</v>
+        <v>7.9960000000000003E-2</v>
       </c>
       <c r="H46">
         <v>60.9375</v>
@@ -1457,2050 +1457,2050 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>7.8210000000000002E-2</v>
+        <v>7.986E-2</v>
       </c>
       <c r="B47">
-        <v>59.375</v>
+        <v>60.9375</v>
       </c>
       <c r="C47">
-        <v>7.8210000000000002E-2</v>
+        <v>7.9799999999999996E-2</v>
       </c>
       <c r="D47">
-        <v>59.375</v>
+        <v>60.9375</v>
       </c>
       <c r="E47">
-        <v>7.8179999999999999E-2</v>
+        <v>8.0060000000000006E-2</v>
       </c>
       <c r="F47">
-        <v>59.375</v>
+        <v>60.9375</v>
       </c>
       <c r="G47">
-        <v>7.7920000000000003E-2</v>
+        <v>7.9689999999999997E-2</v>
       </c>
       <c r="H47">
-        <v>59.375</v>
+        <v>60.9375</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>7.6139999999999999E-2</v>
+        <v>7.7799999999999994E-2</v>
       </c>
       <c r="B48">
-        <v>57.8125</v>
+        <v>59.375</v>
       </c>
       <c r="C48">
-        <v>7.6139999999999999E-2</v>
+        <v>7.7740000000000004E-2</v>
       </c>
       <c r="D48">
-        <v>57.8125</v>
+        <v>59.375</v>
       </c>
       <c r="E48">
-        <v>7.6119999999999993E-2</v>
+        <v>7.7990000000000004E-2</v>
       </c>
       <c r="F48">
-        <v>57.8125</v>
+        <v>59.375</v>
       </c>
       <c r="G48">
-        <v>7.5859999999999997E-2</v>
+        <v>7.7630000000000005E-2</v>
       </c>
       <c r="H48">
-        <v>57.8125</v>
+        <v>59.375</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>7.4090000000000003E-2</v>
+        <v>7.5749999999999998E-2</v>
       </c>
       <c r="B49">
-        <v>56.25</v>
+        <v>57.8125</v>
       </c>
       <c r="C49">
-        <v>7.4090000000000003E-2</v>
+        <v>7.5679999999999997E-2</v>
       </c>
       <c r="D49">
-        <v>56.25</v>
+        <v>57.8125</v>
       </c>
       <c r="E49">
-        <v>7.4060000000000001E-2</v>
+        <v>7.5939999999999994E-2</v>
       </c>
       <c r="F49">
-        <v>56.25</v>
+        <v>57.8125</v>
       </c>
       <c r="G49">
-        <v>7.3819999999999997E-2</v>
+        <v>7.5579999999999994E-2</v>
       </c>
       <c r="H49">
-        <v>56.25</v>
+        <v>57.8125</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>7.2029999999999997E-2</v>
+        <v>7.3690000000000005E-2</v>
       </c>
       <c r="B50">
-        <v>54.6875</v>
+        <v>56.25</v>
       </c>
       <c r="C50">
-        <v>7.2029999999999997E-2</v>
+        <v>7.3639999999999997E-2</v>
       </c>
       <c r="D50">
-        <v>54.6875</v>
+        <v>56.25</v>
       </c>
       <c r="E50">
-        <v>7.2010000000000005E-2</v>
+        <v>7.3870000000000005E-2</v>
       </c>
       <c r="F50">
-        <v>54.6875</v>
+        <v>56.25</v>
       </c>
       <c r="G50">
-        <v>7.177E-2</v>
+        <v>7.3550000000000004E-2</v>
       </c>
       <c r="H50">
-        <v>54.6875</v>
+        <v>56.25</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>6.9980000000000001E-2</v>
+        <v>7.1639999999999995E-2</v>
       </c>
       <c r="B51">
-        <v>53.125</v>
+        <v>54.6875</v>
       </c>
       <c r="C51">
-        <v>6.9980000000000001E-2</v>
+        <v>7.1580000000000005E-2</v>
       </c>
       <c r="D51">
-        <v>53.125</v>
+        <v>54.6875</v>
       </c>
       <c r="E51">
-        <v>6.9949999999999998E-2</v>
+        <v>7.1819999999999995E-2</v>
       </c>
       <c r="F51">
-        <v>53.125</v>
+        <v>54.6875</v>
       </c>
       <c r="G51">
-        <v>6.973E-2</v>
+        <v>7.152E-2</v>
       </c>
       <c r="H51">
-        <v>53.125</v>
+        <v>54.6875</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>6.7909999999999998E-2</v>
+        <v>6.9589999999999999E-2</v>
       </c>
       <c r="B52">
-        <v>51.5625</v>
+        <v>53.125</v>
       </c>
       <c r="C52">
-        <v>6.7919999999999994E-2</v>
+        <v>6.9529999999999995E-2</v>
       </c>
       <c r="D52">
-        <v>51.5625</v>
+        <v>53.125</v>
       </c>
       <c r="E52">
-        <v>6.7900000000000002E-2</v>
+        <v>6.9750000000000006E-2</v>
       </c>
       <c r="F52">
-        <v>51.5625</v>
+        <v>53.125</v>
       </c>
       <c r="G52">
-        <v>6.7680000000000004E-2</v>
+        <v>6.9459999999999994E-2</v>
       </c>
       <c r="H52">
-        <v>51.5625</v>
+        <v>53.125</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>6.5869999999999998E-2</v>
+        <v>6.7540000000000003E-2</v>
       </c>
       <c r="B53">
-        <v>50</v>
+        <v>51.5625</v>
       </c>
       <c r="C53">
-        <v>6.5869999999999998E-2</v>
+        <v>6.7489999999999994E-2</v>
       </c>
       <c r="D53">
-        <v>50</v>
+        <v>51.5625</v>
       </c>
       <c r="E53">
-        <v>6.5839999999999996E-2</v>
+        <v>6.7699999999999996E-2</v>
       </c>
       <c r="F53">
-        <v>50</v>
+        <v>51.5625</v>
       </c>
       <c r="G53">
-        <v>6.5629999999999994E-2</v>
+        <v>6.7419999999999994E-2</v>
       </c>
       <c r="H53">
-        <v>50</v>
+        <v>51.5625</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>6.3740000000000005E-2</v>
+        <v>6.5420000000000006E-2</v>
       </c>
       <c r="B54">
-        <v>48.4375</v>
+        <v>50</v>
       </c>
       <c r="C54">
-        <v>6.3740000000000005E-2</v>
+        <v>6.5360000000000001E-2</v>
       </c>
       <c r="D54">
-        <v>48.4375</v>
+        <v>50</v>
       </c>
       <c r="E54">
-        <v>6.3719999999999999E-2</v>
+        <v>6.5579999999999999E-2</v>
       </c>
       <c r="F54">
-        <v>48.4375</v>
+        <v>50</v>
       </c>
       <c r="G54">
-        <v>6.3519999999999993E-2</v>
+        <v>6.5299999999999997E-2</v>
       </c>
       <c r="H54">
-        <v>48.4375</v>
+        <v>50</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>6.1690000000000002E-2</v>
+        <v>6.336E-2</v>
       </c>
       <c r="B55">
-        <v>46.875</v>
+        <v>48.4375</v>
       </c>
       <c r="C55">
-        <v>6.1690000000000002E-2</v>
+        <v>6.3320000000000001E-2</v>
       </c>
       <c r="D55">
-        <v>46.875</v>
+        <v>48.4375</v>
       </c>
       <c r="E55">
-        <v>6.1670000000000003E-2</v>
+        <v>6.3519999999999993E-2</v>
       </c>
       <c r="F55">
-        <v>46.875</v>
+        <v>48.4375</v>
       </c>
       <c r="G55">
-        <v>6.148E-2</v>
+        <v>6.3250000000000001E-2</v>
       </c>
       <c r="H55">
-        <v>46.875</v>
+        <v>48.4375</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>5.9630000000000002E-2</v>
+        <v>6.1310000000000003E-2</v>
       </c>
       <c r="B56">
-        <v>45.3125</v>
+        <v>46.875</v>
       </c>
       <c r="C56">
-        <v>5.9630000000000002E-2</v>
+        <v>6.1249999999999999E-2</v>
       </c>
       <c r="D56">
-        <v>45.3125</v>
+        <v>46.875</v>
       </c>
       <c r="E56">
-        <v>5.9610000000000003E-2</v>
+        <v>6.1460000000000001E-2</v>
       </c>
       <c r="F56">
-        <v>45.3125</v>
+        <v>46.875</v>
       </c>
       <c r="G56">
-        <v>5.9420000000000001E-2</v>
+        <v>6.1199999999999997E-2</v>
       </c>
       <c r="H56">
-        <v>45.3125</v>
+        <v>46.875</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>5.7579999999999999E-2</v>
+        <v>5.926E-2</v>
       </c>
       <c r="B57">
-        <v>43.75</v>
+        <v>45.3125</v>
       </c>
       <c r="C57">
-        <v>5.7579999999999999E-2</v>
+        <v>5.9209999999999999E-2</v>
       </c>
       <c r="D57">
-        <v>43.75</v>
+        <v>45.3125</v>
       </c>
       <c r="E57">
-        <v>5.756E-2</v>
+        <v>5.9400000000000001E-2</v>
       </c>
       <c r="F57">
-        <v>43.75</v>
+        <v>45.3125</v>
       </c>
       <c r="G57">
-        <v>5.738E-2</v>
+        <v>5.9150000000000001E-2</v>
       </c>
       <c r="H57">
-        <v>43.75</v>
+        <v>45.3125</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>5.5539999999999999E-2</v>
+        <v>5.7200000000000001E-2</v>
       </c>
       <c r="B58">
-        <v>42.1875</v>
+        <v>43.75</v>
       </c>
       <c r="C58">
-        <v>5.5539999999999999E-2</v>
+        <v>5.7160000000000002E-2</v>
       </c>
       <c r="D58">
-        <v>42.1875</v>
+        <v>43.75</v>
       </c>
       <c r="E58">
-        <v>5.5509999999999997E-2</v>
+        <v>5.7349999999999998E-2</v>
       </c>
       <c r="F58">
-        <v>42.1875</v>
+        <v>43.75</v>
       </c>
       <c r="G58">
-        <v>5.534E-2</v>
+        <v>5.7110000000000001E-2</v>
       </c>
       <c r="H58">
-        <v>42.1875</v>
+        <v>43.75</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>5.348E-2</v>
+        <v>5.5160000000000001E-2</v>
       </c>
       <c r="B59">
-        <v>40.625</v>
+        <v>42.1875</v>
       </c>
       <c r="C59">
-        <v>5.348E-2</v>
+        <v>5.5120000000000002E-2</v>
       </c>
       <c r="D59">
-        <v>40.625</v>
+        <v>42.1875</v>
       </c>
       <c r="E59">
-        <v>5.3469999999999997E-2</v>
+        <v>5.5289999999999999E-2</v>
       </c>
       <c r="F59">
-        <v>40.625</v>
+        <v>42.1875</v>
       </c>
       <c r="G59">
-        <v>1.64E-3</v>
+        <v>5.5059999999999998E-2</v>
       </c>
       <c r="H59">
-        <v>40.625</v>
+        <v>42.1875</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>5.1429999999999997E-2</v>
+        <v>5.3100000000000001E-2</v>
       </c>
       <c r="B60">
-        <v>39.0625</v>
+        <v>40.625</v>
       </c>
       <c r="C60">
-        <v>5.1429999999999997E-2</v>
+        <v>5.3060000000000003E-2</v>
       </c>
       <c r="D60">
-        <v>39.0625</v>
+        <v>40.625</v>
       </c>
       <c r="E60">
-        <v>5.1400000000000001E-2</v>
+        <v>5.3220000000000003E-2</v>
       </c>
       <c r="F60">
-        <v>39.0625</v>
+        <v>40.625</v>
       </c>
       <c r="G60">
-        <v>0</v>
+        <v>5.3010000000000002E-2</v>
       </c>
       <c r="H60">
-        <v>39.0625</v>
+        <v>40.625</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>4.9369999999999997E-2</v>
+        <v>5.1049999999999998E-2</v>
       </c>
       <c r="B61">
-        <v>37.5</v>
+        <v>39.0625</v>
       </c>
       <c r="C61">
-        <v>4.9369999999999997E-2</v>
+        <v>5.101E-2</v>
       </c>
       <c r="D61">
-        <v>37.5</v>
+        <v>39.0625</v>
       </c>
       <c r="E61">
-        <v>4.9349999999999998E-2</v>
+        <v>5.1180000000000003E-2</v>
       </c>
       <c r="F61">
-        <v>37.5</v>
+        <v>39.0625</v>
       </c>
       <c r="G61">
-        <v>0</v>
+        <v>5.0970000000000001E-2</v>
       </c>
       <c r="H61">
-        <v>37.5</v>
+        <v>39.0625</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>4.7309999999999998E-2</v>
+        <v>4.8980000000000003E-2</v>
       </c>
       <c r="B62">
-        <v>35.9375</v>
+        <v>37.5</v>
       </c>
       <c r="C62">
-        <v>4.7309999999999998E-2</v>
+        <v>4.895E-2</v>
       </c>
       <c r="D62">
-        <v>35.9375</v>
+        <v>37.5</v>
       </c>
       <c r="E62">
-        <v>4.7280000000000003E-2</v>
+        <v>4.9099999999999998E-2</v>
       </c>
       <c r="F62">
-        <v>35.9375</v>
+        <v>37.5</v>
       </c>
       <c r="G62">
-        <v>0</v>
+        <v>4.8899999999999999E-2</v>
       </c>
       <c r="H62">
-        <v>35.9375</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>4.5249999999999999E-2</v>
+        <v>4.6940000000000003E-2</v>
       </c>
       <c r="B63">
-        <v>34.375</v>
+        <v>35.9375</v>
       </c>
       <c r="C63">
-        <v>4.5249999999999999E-2</v>
+        <v>4.6890000000000001E-2</v>
       </c>
       <c r="D63">
-        <v>34.375</v>
+        <v>35.9375</v>
       </c>
       <c r="E63">
-        <v>3.3300000000000003E-2</v>
+        <v>4.7050000000000002E-2</v>
       </c>
       <c r="F63">
-        <v>34.375</v>
+        <v>35.9375</v>
       </c>
       <c r="G63">
-        <v>0</v>
+        <v>4.6859999999999999E-2</v>
       </c>
       <c r="H63">
-        <v>34.375</v>
+        <v>35.9375</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>4.3200000000000002E-2</v>
+        <v>4.4880000000000003E-2</v>
       </c>
       <c r="B64">
-        <v>32.8125</v>
+        <v>34.375</v>
       </c>
       <c r="C64">
-        <v>4.3200000000000002E-2</v>
+        <v>4.4839999999999998E-2</v>
       </c>
       <c r="D64">
-        <v>32.8125</v>
+        <v>34.375</v>
       </c>
       <c r="E64" s="1">
-        <v>6.7005499999999994E-5</v>
+        <v>4.4990000000000002E-2</v>
       </c>
       <c r="F64">
-        <v>32.8125</v>
+        <v>34.375</v>
       </c>
       <c r="G64">
-        <v>0</v>
+        <v>4.48E-2</v>
       </c>
       <c r="H64">
-        <v>32.8125</v>
+        <v>34.375</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>4.1149999999999999E-2</v>
+        <v>4.2840000000000003E-2</v>
       </c>
       <c r="B65">
-        <v>31.25</v>
+        <v>32.8125</v>
       </c>
       <c r="C65">
-        <v>4.1149999999999999E-2</v>
+        <v>4.2810000000000001E-2</v>
       </c>
       <c r="D65">
-        <v>31.25</v>
+        <v>32.8125</v>
       </c>
       <c r="E65" s="1">
-        <v>3.35028E-5</v>
+        <v>4.2939999999999999E-2</v>
       </c>
       <c r="F65">
-        <v>31.25</v>
+        <v>32.8125</v>
       </c>
       <c r="G65">
-        <v>0</v>
+        <v>4.2770000000000002E-2</v>
       </c>
       <c r="H65">
-        <v>31.25</v>
+        <v>32.8125</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>3.9100000000000003E-2</v>
+        <v>4.0800000000000003E-2</v>
       </c>
       <c r="B66">
-        <v>29.6875</v>
+        <v>31.25</v>
       </c>
       <c r="C66">
-        <v>3.9100000000000003E-2</v>
+        <v>4.0750000000000001E-2</v>
       </c>
       <c r="D66">
-        <v>29.6875</v>
+        <v>31.25</v>
       </c>
       <c r="E66" s="1">
-        <v>1.11676E-5</v>
+        <v>4.088E-2</v>
       </c>
       <c r="F66">
-        <v>29.6875</v>
+        <v>31.25</v>
       </c>
       <c r="G66">
-        <v>0</v>
+        <v>4.0730000000000002E-2</v>
       </c>
       <c r="H66">
-        <v>29.6875</v>
+        <v>31.25</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>3.7039999999999997E-2</v>
+        <v>3.8739999999999997E-2</v>
       </c>
       <c r="B67">
-        <v>28.125</v>
+        <v>29.6875</v>
       </c>
       <c r="C67">
-        <v>3.7039999999999997E-2</v>
+        <v>3.8710000000000001E-2</v>
       </c>
       <c r="D67">
-        <v>28.125</v>
+        <v>29.6875</v>
       </c>
       <c r="E67" s="1">
-        <v>1.11676E-5</v>
+        <v>3.884E-2</v>
       </c>
       <c r="F67">
-        <v>28.125</v>
+        <v>29.6875</v>
       </c>
       <c r="G67">
-        <v>0</v>
+        <v>3.8670000000000003E-2</v>
       </c>
       <c r="H67">
-        <v>28.125</v>
+        <v>29.6875</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>3.499E-2</v>
+        <v>3.669E-2</v>
       </c>
       <c r="B68">
-        <v>26.5625</v>
+        <v>28.125</v>
       </c>
       <c r="C68">
-        <v>3.499E-2</v>
+        <v>3.6650000000000002E-2</v>
       </c>
       <c r="D68">
-        <v>26.5625</v>
+        <v>28.125</v>
       </c>
       <c r="E68" s="1">
-        <v>1.11676E-5</v>
+        <v>3.6769999999999997E-2</v>
       </c>
       <c r="F68">
-        <v>26.5625</v>
+        <v>28.125</v>
       </c>
       <c r="G68">
-        <v>0</v>
+        <v>3.6630000000000003E-2</v>
       </c>
       <c r="H68">
-        <v>26.5625</v>
+        <v>28.125</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>3.2930000000000001E-2</v>
+        <v>3.4639999999999997E-2</v>
       </c>
       <c r="B69">
-        <v>25</v>
+        <v>26.5625</v>
       </c>
       <c r="C69">
-        <v>1.436E-2</v>
+        <v>3.4610000000000002E-2</v>
       </c>
       <c r="D69">
-        <v>25</v>
+        <v>26.5625</v>
       </c>
       <c r="E69" s="1">
-        <v>1.11676E-5</v>
+        <v>3.4720000000000001E-2</v>
       </c>
       <c r="F69">
-        <v>25</v>
+        <v>26.5625</v>
       </c>
       <c r="G69">
-        <v>0</v>
+        <v>3.4590000000000003E-2</v>
       </c>
       <c r="H69">
-        <v>25</v>
+        <v>26.5625</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>3.0890000000000001E-2</v>
+        <v>3.2599999999999997E-2</v>
       </c>
       <c r="B70">
-        <v>23.4375</v>
+        <v>25</v>
       </c>
       <c r="C70" s="1">
-        <v>1.3401099999999999E-4</v>
+        <v>3.2559999999999999E-2</v>
       </c>
       <c r="D70">
-        <v>23.4375</v>
+        <v>25</v>
       </c>
       <c r="E70" s="1">
-        <v>1.11676E-5</v>
+        <v>3.2669999999999998E-2</v>
       </c>
       <c r="F70">
-        <v>23.4375</v>
+        <v>25</v>
       </c>
       <c r="G70">
-        <v>0</v>
+        <v>3.2539999999999999E-2</v>
       </c>
       <c r="H70">
-        <v>23.4375</v>
+        <v>25</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>2.8830000000000001E-2</v>
+        <v>3.0550000000000001E-2</v>
       </c>
       <c r="B71">
-        <v>21.875</v>
+        <v>23.4375</v>
       </c>
       <c r="C71" s="1">
-        <v>5.5837900000000003E-5</v>
+        <v>3.0519999999999999E-2</v>
       </c>
       <c r="D71">
-        <v>21.875</v>
+        <v>23.4375</v>
       </c>
       <c r="E71" s="1">
-        <v>1.11676E-5</v>
+        <v>3.0620000000000001E-2</v>
       </c>
       <c r="F71">
-        <v>21.875</v>
+        <v>23.4375</v>
       </c>
       <c r="G71">
-        <v>0</v>
+        <v>3.0499999999999999E-2</v>
       </c>
       <c r="H71">
-        <v>21.875</v>
+        <v>23.4375</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>2.6780000000000002E-2</v>
+        <v>2.8500000000000001E-2</v>
       </c>
       <c r="B72">
-        <v>20.3125</v>
+        <v>21.875</v>
       </c>
       <c r="C72" s="1">
-        <v>2.2335199999999999E-5</v>
+        <v>2.8469999999999999E-2</v>
       </c>
       <c r="D72">
-        <v>20.3125</v>
+        <v>21.875</v>
       </c>
       <c r="E72" s="1">
-        <v>1.11676E-5</v>
+        <v>2.8559999999999999E-2</v>
       </c>
       <c r="F72">
-        <v>20.3125</v>
+        <v>21.875</v>
       </c>
       <c r="G72">
-        <v>0</v>
+        <v>2.844E-2</v>
       </c>
       <c r="H72">
-        <v>20.3125</v>
+        <v>21.875</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>2.4729999999999999E-2</v>
+        <v>2.6440000000000002E-2</v>
       </c>
       <c r="B73">
-        <v>18.75</v>
+        <v>20.3125</v>
       </c>
       <c r="C73" s="1">
-        <v>1.11676E-5</v>
+        <v>2.6419999999999999E-2</v>
       </c>
       <c r="D73">
-        <v>18.75</v>
+        <v>20.3125</v>
       </c>
       <c r="E73" s="1">
-        <v>1.11676E-5</v>
+        <v>2.6499999999999999E-2</v>
       </c>
       <c r="F73">
-        <v>18.75</v>
+        <v>20.3125</v>
       </c>
       <c r="G73">
-        <v>0</v>
+        <v>2.64E-2</v>
       </c>
       <c r="H73">
-        <v>18.75</v>
+        <v>20.3125</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>2.2669999999999999E-2</v>
+        <v>2.4400000000000002E-2</v>
       </c>
       <c r="B74">
-        <v>17.1875</v>
+        <v>18.75</v>
       </c>
       <c r="C74" s="1">
-        <v>1.11676E-5</v>
+        <v>2.4379999999999999E-2</v>
       </c>
       <c r="D74">
-        <v>17.1875</v>
+        <v>18.75</v>
       </c>
       <c r="E74" s="1">
-        <v>1.11676E-5</v>
+        <v>2.445E-2</v>
       </c>
       <c r="F74">
-        <v>17.1875</v>
+        <v>18.75</v>
       </c>
       <c r="G74">
-        <v>0</v>
+        <v>2.435E-2</v>
       </c>
       <c r="H74">
-        <v>17.1875</v>
+        <v>18.75</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75">
-        <v>2.0619999999999999E-2</v>
+        <v>2.2360000000000001E-2</v>
       </c>
       <c r="B75">
-        <v>15.625</v>
+        <v>17.1875</v>
       </c>
       <c r="C75" s="1">
-        <v>1.11676E-5</v>
+        <v>2.232E-2</v>
       </c>
       <c r="D75">
-        <v>15.625</v>
+        <v>17.1875</v>
       </c>
       <c r="E75" s="1">
-        <v>1.11676E-5</v>
+        <v>2.2349999999999998E-2</v>
       </c>
       <c r="F75">
-        <v>15.625</v>
+        <v>17.1875</v>
       </c>
       <c r="G75">
-        <v>0</v>
+        <v>2.1899999999999999E-2</v>
       </c>
       <c r="H75">
-        <v>15.625</v>
+        <v>17.1875</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>1.856E-2</v>
+        <v>2.0289999999999999E-2</v>
       </c>
       <c r="B76">
-        <v>14.0625</v>
+        <v>15.625</v>
       </c>
       <c r="C76" s="1">
-        <v>1.11676E-5</v>
+        <v>2.0250000000000001E-2</v>
       </c>
       <c r="D76">
-        <v>14.0625</v>
+        <v>15.625</v>
       </c>
       <c r="E76" s="1">
-        <v>1.11676E-5</v>
+        <v>1.8540000000000001E-2</v>
       </c>
       <c r="F76">
-        <v>14.0625</v>
+        <v>15.625</v>
       </c>
       <c r="G76">
-        <v>0</v>
+        <v>4.3600000000000002E-3</v>
       </c>
       <c r="H76">
-        <v>14.0625</v>
+        <v>15.625</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>1.6480000000000002E-2</v>
+        <v>1.8249999999999999E-2</v>
       </c>
       <c r="B77">
-        <v>12.5</v>
+        <v>14.0625</v>
       </c>
       <c r="C77" s="1">
-        <v>1.11676E-5</v>
+        <v>1.7729999999999999E-2</v>
       </c>
       <c r="D77">
-        <v>12.5</v>
+        <v>14.0625</v>
       </c>
       <c r="E77" s="1">
-        <v>1.11676E-5</v>
+        <v>1.5E-3</v>
       </c>
       <c r="F77">
-        <v>12.5</v>
+        <v>14.0625</v>
       </c>
       <c r="G77">
         <v>0</v>
       </c>
       <c r="H77">
-        <v>12.5</v>
+        <v>14.0625</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>1.4030000000000001E-2</v>
+        <v>1.619E-2</v>
       </c>
       <c r="B78">
-        <v>10.9375</v>
+        <v>12.5</v>
       </c>
       <c r="C78" s="1">
-        <v>1.11676E-5</v>
+        <v>7.1500000000000001E-3</v>
       </c>
       <c r="D78">
-        <v>10.9375</v>
+        <v>12.5</v>
       </c>
       <c r="E78" s="1">
         <v>1.11676E-5</v>
       </c>
       <c r="F78">
-        <v>10.9375</v>
+        <v>12.5</v>
       </c>
       <c r="G78">
         <v>0</v>
       </c>
       <c r="H78">
-        <v>10.9375</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79">
-        <v>7.43E-3</v>
+        <v>1.414E-2</v>
       </c>
       <c r="B79">
-        <v>9.375</v>
+        <v>10.9375</v>
       </c>
       <c r="C79" s="1">
-        <v>1.11676E-5</v>
+        <v>1.1167600000000001E-4</v>
       </c>
       <c r="D79">
-        <v>9.375</v>
+        <v>10.9375</v>
       </c>
       <c r="E79" s="1">
-        <v>1.11676E-5</v>
+        <v>0</v>
       </c>
       <c r="F79">
-        <v>9.375</v>
+        <v>10.9375</v>
       </c>
       <c r="G79">
         <v>0</v>
       </c>
       <c r="H79">
-        <v>9.375</v>
+        <v>10.9375</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>1.9499999999999999E-3</v>
+        <v>1.205E-2</v>
       </c>
       <c r="B80">
-        <v>7.8125</v>
+        <v>9.375</v>
       </c>
       <c r="C80" s="1">
-        <v>1.11676E-5</v>
+        <v>2.2335199999999999E-5</v>
       </c>
       <c r="D80">
-        <v>7.8125</v>
+        <v>9.375</v>
       </c>
       <c r="E80" s="1">
         <v>1.11676E-5</v>
       </c>
       <c r="F80">
-        <v>7.8125</v>
+        <v>9.375</v>
       </c>
       <c r="G80">
         <v>0</v>
       </c>
       <c r="H80">
-        <v>7.8125</v>
+        <v>9.375</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
-        <v>7.8173100000000003E-4</v>
+        <v>9.7900000000000001E-3</v>
       </c>
       <c r="B81">
-        <v>6.25</v>
+        <v>7.8125</v>
       </c>
       <c r="C81" s="1">
         <v>1.11676E-5</v>
       </c>
       <c r="D81">
-        <v>6.25</v>
+        <v>7.8125</v>
       </c>
       <c r="E81" s="1">
         <v>1.11676E-5</v>
       </c>
       <c r="F81">
-        <v>6.25</v>
+        <v>7.8125</v>
       </c>
       <c r="G81">
         <v>0</v>
       </c>
       <c r="H81">
-        <v>6.25</v>
+        <v>7.8125</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
-        <v>3.2385999999999998E-4</v>
+        <v>7.0499999999999998E-3</v>
       </c>
       <c r="B82">
-        <v>4.6875</v>
+        <v>6.25</v>
       </c>
       <c r="C82" s="1">
         <v>1.11676E-5</v>
       </c>
       <c r="D82">
-        <v>4.6875</v>
+        <v>6.25</v>
       </c>
       <c r="E82" s="1">
         <v>1.11676E-5</v>
       </c>
       <c r="F82">
-        <v>4.6875</v>
+        <v>6.25</v>
       </c>
       <c r="G82">
         <v>0</v>
       </c>
       <c r="H82">
-        <v>4.6875</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
-        <v>1.0050799999999999E-4</v>
+        <v>3.98E-3</v>
       </c>
       <c r="B83">
-        <v>3.125</v>
+        <v>4.6875</v>
       </c>
       <c r="C83" s="1">
         <v>1.11676E-5</v>
       </c>
       <c r="D83">
-        <v>3.125</v>
+        <v>4.6875</v>
       </c>
       <c r="E83" s="1">
         <v>1.11676E-5</v>
       </c>
       <c r="F83">
-        <v>3.125</v>
+        <v>4.6875</v>
       </c>
       <c r="G83">
         <v>0</v>
       </c>
       <c r="H83">
-        <v>3.125</v>
+        <v>4.6875</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
-        <v>1.11676E-5</v>
+        <v>1.73E-3</v>
       </c>
       <c r="B84">
+        <v>3.125</v>
+      </c>
+      <c r="C84" s="1">
+        <v>1.11676E-5</v>
+      </c>
+      <c r="D84">
+        <v>3.125</v>
+      </c>
+      <c r="E84" s="1">
+        <v>1.11676E-5</v>
+      </c>
+      <c r="F84">
+        <v>3.125</v>
+      </c>
+      <c r="G84">
+        <v>0</v>
+      </c>
+      <c r="H84">
+        <v>3.125</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" s="1">
+        <v>5.0254100000000001E-4</v>
+      </c>
+      <c r="B85">
         <v>1.5625</v>
       </c>
-      <c r="C84" s="1">
-        <v>1.11676E-5</v>
-      </c>
-      <c r="D84">
+      <c r="C85" s="1">
+        <v>1.11676E-5</v>
+      </c>
+      <c r="D85">
         <v>1.5625</v>
       </c>
-      <c r="E84" s="1">
-        <v>1.11676E-5</v>
-      </c>
-      <c r="F84">
+      <c r="E85" s="1">
+        <v>1.11676E-5</v>
+      </c>
+      <c r="F85">
         <v>1.5625</v>
       </c>
-      <c r="G84">
-        <v>0</v>
-      </c>
-      <c r="H84">
+      <c r="G85">
+        <v>0</v>
+      </c>
+      <c r="H85">
         <v>1.5625</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A85">
-        <v>0</v>
-      </c>
-      <c r="B85">
-        <v>0</v>
-      </c>
-      <c r="C85" s="1">
-        <v>1.11676E-5</v>
-      </c>
-      <c r="D85">
-        <v>0</v>
-      </c>
-      <c r="E85" s="1">
-        <v>1.11676E-5</v>
-      </c>
-      <c r="F85">
-        <v>0</v>
-      </c>
-      <c r="G85">
-        <v>0</v>
-      </c>
-      <c r="H85">
-        <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
-        <v>-8.4873700000000002E-4</v>
+        <v>0</v>
       </c>
       <c r="B86">
+        <v>0</v>
+      </c>
+      <c r="C86" s="1">
+        <v>1.11676E-5</v>
+      </c>
+      <c r="D86">
+        <v>0</v>
+      </c>
+      <c r="E86" s="1">
+        <v>1.11676E-5</v>
+      </c>
+      <c r="F86">
+        <v>0</v>
+      </c>
+      <c r="G86">
+        <v>0</v>
+      </c>
+      <c r="H86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" s="1">
+        <v>-4.9137400000000004E-4</v>
+      </c>
+      <c r="B87">
         <v>-1.5625</v>
       </c>
-      <c r="C86">
-        <v>0</v>
-      </c>
-      <c r="D86">
+      <c r="C87" s="1">
+        <v>1.11676E-5</v>
+      </c>
+      <c r="D87">
         <v>-1.5625</v>
       </c>
-      <c r="E86" s="1">
-        <v>1.11676E-5</v>
-      </c>
-      <c r="F86">
+      <c r="E87" s="1">
+        <v>1.11676E-5</v>
+      </c>
+      <c r="F87">
         <v>-1.5625</v>
       </c>
-      <c r="G86">
-        <v>0</v>
-      </c>
-      <c r="H86">
+      <c r="G87">
+        <v>0</v>
+      </c>
+      <c r="H87">
         <v>-1.5625</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A87">
-        <v>-2.5200000000000001E-3</v>
-      </c>
-      <c r="B87">
-        <v>-3.125</v>
-      </c>
-      <c r="C87">
-        <v>0</v>
-      </c>
-      <c r="D87">
-        <v>-3.125</v>
-      </c>
-      <c r="E87" s="1">
-        <v>1.11676E-5</v>
-      </c>
-      <c r="F87">
-        <v>-3.125</v>
-      </c>
-      <c r="G87">
-        <v>0</v>
-      </c>
-      <c r="H87">
-        <v>-3.125</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88">
-        <v>-4.9500000000000004E-3</v>
+        <v>-1.3799999999999999E-3</v>
       </c>
       <c r="B88">
-        <v>-4.6875</v>
-      </c>
-      <c r="C88">
-        <v>0</v>
+        <v>-3.125</v>
+      </c>
+      <c r="C88" s="1">
+        <v>1.11676E-5</v>
       </c>
       <c r="D88">
-        <v>-4.6875</v>
+        <v>-3.125</v>
       </c>
       <c r="E88" s="1">
         <v>1.11676E-5</v>
       </c>
       <c r="F88">
-        <v>-4.6875</v>
+        <v>-3.125</v>
       </c>
       <c r="G88">
         <v>0</v>
       </c>
       <c r="H88">
-        <v>-4.6875</v>
+        <v>-3.125</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89">
-        <v>-7.5799999999999999E-3</v>
+        <v>-2.9499999999999999E-3</v>
       </c>
       <c r="B89">
-        <v>-6.25</v>
-      </c>
-      <c r="C89">
-        <v>0</v>
+        <v>-4.6875</v>
+      </c>
+      <c r="C89" s="1">
+        <v>1.11676E-5</v>
       </c>
       <c r="D89">
-        <v>-6.25</v>
+        <v>-4.6875</v>
       </c>
       <c r="E89" s="1">
         <v>1.11676E-5</v>
       </c>
       <c r="F89">
-        <v>-6.25</v>
+        <v>-4.6875</v>
       </c>
       <c r="G89">
         <v>0</v>
       </c>
       <c r="H89">
-        <v>-6.25</v>
+        <v>-4.6875</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90">
-        <v>-9.9399999999999992E-3</v>
+        <v>-5.7000000000000002E-3</v>
       </c>
       <c r="B90">
-        <v>-7.8125</v>
+        <v>-6.25</v>
       </c>
       <c r="C90" s="1">
-        <v>-1.11676E-5</v>
+        <v>1.11676E-5</v>
       </c>
       <c r="D90">
-        <v>-7.8125</v>
+        <v>-6.25</v>
       </c>
       <c r="E90" s="1">
         <v>1.11676E-5</v>
       </c>
       <c r="F90">
-        <v>-7.8125</v>
+        <v>-6.25</v>
       </c>
       <c r="G90">
         <v>0</v>
       </c>
       <c r="H90">
-        <v>-7.8125</v>
+        <v>-6.25</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91">
-        <v>-1.2070000000000001E-2</v>
+        <v>-9.2999999999999992E-3</v>
       </c>
       <c r="B91">
-        <v>-9.375</v>
+        <v>-7.8125</v>
       </c>
       <c r="C91" s="1">
-        <v>-4.4670299999999998E-5</v>
+        <v>1.11676E-5</v>
       </c>
       <c r="D91">
-        <v>-9.375</v>
+        <v>-7.8125</v>
       </c>
       <c r="E91" s="1">
         <v>1.11676E-5</v>
       </c>
       <c r="F91">
-        <v>-9.375</v>
+        <v>-7.8125</v>
       </c>
       <c r="G91">
         <v>0</v>
       </c>
       <c r="H91">
-        <v>-9.375</v>
+        <v>-7.8125</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92">
-        <v>-1.4149999999999999E-2</v>
+        <v>-1.2120000000000001E-2</v>
       </c>
       <c r="B92">
-        <v>-10.9375</v>
+        <v>-9.375</v>
       </c>
       <c r="C92" s="1">
-        <v>-8.9340700000000003E-4</v>
+        <v>1.11676E-5</v>
       </c>
       <c r="D92">
-        <v>-10.9375</v>
+        <v>-9.375</v>
       </c>
       <c r="E92" s="1">
         <v>1.11676E-5</v>
       </c>
       <c r="F92">
-        <v>-10.9375</v>
+        <v>-9.375</v>
       </c>
       <c r="G92">
         <v>0</v>
       </c>
       <c r="H92">
-        <v>-10.9375</v>
+        <v>-9.375</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93">
-        <v>-1.6199999999999999E-2</v>
+        <v>-1.435E-2</v>
       </c>
       <c r="B93">
-        <v>-12.5</v>
+        <v>-10.9375</v>
       </c>
       <c r="C93">
-        <v>-1.2109999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="D93">
-        <v>-12.5</v>
+        <v>-10.9375</v>
       </c>
       <c r="E93" s="1">
         <v>1.11676E-5</v>
       </c>
       <c r="F93">
-        <v>-12.5</v>
+        <v>-10.9375</v>
       </c>
       <c r="G93">
         <v>0</v>
       </c>
       <c r="H93">
-        <v>-12.5</v>
+        <v>-10.9375</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94">
-        <v>-1.8270000000000002E-2</v>
+        <v>-1.6420000000000001E-2</v>
       </c>
       <c r="B94">
-        <v>-14.0625</v>
+        <v>-12.5</v>
       </c>
       <c r="C94">
-        <v>-1.7950000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="D94">
-        <v>-14.0625</v>
-      </c>
-      <c r="E94">
-        <v>-3.3300000000000001E-3</v>
+        <v>-12.5</v>
+      </c>
+      <c r="E94" s="1">
+        <v>1.11676E-5</v>
       </c>
       <c r="F94">
-        <v>-14.0625</v>
+        <v>-12.5</v>
       </c>
       <c r="G94">
         <v>0</v>
       </c>
       <c r="H94">
-        <v>-14.0625</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95">
-        <v>-2.0310000000000002E-2</v>
+        <v>-1.848E-2</v>
       </c>
       <c r="B95">
-        <v>-15.625</v>
-      </c>
-      <c r="C95">
-        <v>-2.0299999999999999E-2</v>
+        <v>-14.0625</v>
+      </c>
+      <c r="C95" s="1">
+        <v>-2.2335199999999999E-5</v>
       </c>
       <c r="D95">
-        <v>-15.625</v>
-      </c>
-      <c r="E95">
-        <v>-1.9400000000000001E-2</v>
+        <v>-14.0625</v>
+      </c>
+      <c r="E95" s="1">
+        <v>1.11676E-5</v>
       </c>
       <c r="F95">
-        <v>-15.625</v>
+        <v>-14.0625</v>
       </c>
       <c r="G95">
-        <v>-7.8200000000000006E-3</v>
+        <v>0</v>
       </c>
       <c r="H95">
-        <v>-15.625</v>
+        <v>-14.0625</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96">
-        <v>-2.2380000000000001E-2</v>
+        <v>-2.053E-2</v>
       </c>
       <c r="B96">
-        <v>-17.1875</v>
-      </c>
-      <c r="C96">
-        <v>-2.2380000000000001E-2</v>
+        <v>-15.625</v>
+      </c>
+      <c r="C96" s="1">
+        <v>-5.5837900000000003E-5</v>
       </c>
       <c r="D96">
-        <v>-17.1875</v>
-      </c>
-      <c r="E96">
-        <v>-2.2339999999999999E-2</v>
+        <v>-15.625</v>
+      </c>
+      <c r="E96" s="1">
+        <v>1.11676E-5</v>
       </c>
       <c r="F96">
-        <v>-17.1875</v>
+        <v>-15.625</v>
       </c>
       <c r="G96">
-        <v>-2.2110000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="H96">
-        <v>-17.1875</v>
+        <v>-15.625</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97">
-        <v>-2.443E-2</v>
+        <v>-2.2579999999999999E-2</v>
       </c>
       <c r="B97">
-        <v>-18.75</v>
-      </c>
-      <c r="C97">
-        <v>-2.443E-2</v>
+        <v>-17.1875</v>
+      </c>
+      <c r="C97" s="1">
+        <v>-1.3401099999999999E-4</v>
       </c>
       <c r="D97">
-        <v>-18.75</v>
-      </c>
-      <c r="E97">
-        <v>-2.4410000000000001E-2</v>
+        <v>-17.1875</v>
+      </c>
+      <c r="E97" s="1">
+        <v>1.11676E-5</v>
       </c>
       <c r="F97">
-        <v>-18.75</v>
+        <v>-17.1875</v>
       </c>
       <c r="G97">
-        <v>-2.4330000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="H97">
-        <v>-18.75</v>
+        <v>-17.1875</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98">
-        <v>-2.649E-2</v>
+        <v>-2.462E-2</v>
       </c>
       <c r="B98">
-        <v>-20.3125</v>
+        <v>-18.75</v>
       </c>
       <c r="C98">
-        <v>-2.649E-2</v>
+        <v>-1.1339999999999999E-2</v>
       </c>
       <c r="D98">
-        <v>-20.3125</v>
-      </c>
-      <c r="E98">
-        <v>-2.647E-2</v>
+        <v>-18.75</v>
+      </c>
+      <c r="E98" s="1">
+        <v>1.11676E-5</v>
       </c>
       <c r="F98">
-        <v>-20.3125</v>
+        <v>-18.75</v>
       </c>
       <c r="G98">
-        <v>-2.6380000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="H98">
-        <v>-20.3125</v>
+        <v>-18.75</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99">
-        <v>-2.8539999999999999E-2</v>
+        <v>-2.6679999999999999E-2</v>
       </c>
       <c r="B99">
-        <v>-21.875</v>
+        <v>-20.3125</v>
       </c>
       <c r="C99">
-        <v>-2.853E-2</v>
+        <v>-2.5780000000000001E-2</v>
       </c>
       <c r="D99">
-        <v>-21.875</v>
-      </c>
-      <c r="E99">
-        <v>-2.852E-2</v>
+        <v>-20.3125</v>
+      </c>
+      <c r="E99" s="1">
+        <v>1.11676E-5</v>
       </c>
       <c r="F99">
-        <v>-21.875</v>
+        <v>-20.3125</v>
       </c>
       <c r="G99">
-        <v>-2.843E-2</v>
+        <v>0</v>
       </c>
       <c r="H99">
-        <v>-21.875</v>
+        <v>-20.3125</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100">
-        <v>-3.0599999999999999E-2</v>
+        <v>-2.8719999999999999E-2</v>
       </c>
       <c r="B100">
-        <v>-23.4375</v>
+        <v>-21.875</v>
       </c>
       <c r="C100">
-        <v>-3.0599999999999999E-2</v>
+        <v>-2.8680000000000001E-2</v>
       </c>
       <c r="D100">
-        <v>-23.4375</v>
-      </c>
-      <c r="E100">
-        <v>-3.058E-2</v>
+        <v>-21.875</v>
+      </c>
+      <c r="E100" s="1">
+        <v>1.11676E-5</v>
       </c>
       <c r="F100">
-        <v>-23.4375</v>
+        <v>-21.875</v>
       </c>
       <c r="G100">
-        <v>-3.048E-2</v>
+        <v>0</v>
       </c>
       <c r="H100">
-        <v>-23.4375</v>
+        <v>-21.875</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101">
-        <v>-3.2640000000000002E-2</v>
+        <v>-3.0779999999999998E-2</v>
       </c>
       <c r="B101">
-        <v>-25</v>
+        <v>-23.4375</v>
       </c>
       <c r="C101">
-        <v>-3.2640000000000002E-2</v>
+        <v>-3.074E-2</v>
       </c>
       <c r="D101">
-        <v>-25</v>
+        <v>-23.4375</v>
       </c>
       <c r="E101">
-        <v>-3.2620000000000003E-2</v>
+        <v>0</v>
       </c>
       <c r="F101">
-        <v>-25</v>
+        <v>-23.4375</v>
       </c>
       <c r="G101">
-        <v>-3.252E-2</v>
+        <v>0</v>
       </c>
       <c r="H101">
-        <v>-25</v>
+        <v>-23.4375</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102">
-        <v>-3.4700000000000002E-2</v>
+        <v>-3.2820000000000002E-2</v>
       </c>
       <c r="B102">
-        <v>-26.5625</v>
+        <v>-25</v>
       </c>
       <c r="C102">
-        <v>-3.4700000000000002E-2</v>
+        <v>-3.2779999999999997E-2</v>
       </c>
       <c r="D102">
-        <v>-26.5625</v>
+        <v>-25</v>
       </c>
       <c r="E102">
-        <v>-3.4680000000000002E-2</v>
+        <v>0</v>
       </c>
       <c r="F102">
-        <v>-26.5625</v>
+        <v>-25</v>
       </c>
       <c r="G102">
-        <v>-3.456E-2</v>
+        <v>0</v>
       </c>
       <c r="H102">
-        <v>-26.5625</v>
+        <v>-25</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103">
-        <v>-3.6740000000000002E-2</v>
+        <v>-3.4880000000000001E-2</v>
       </c>
       <c r="B103">
-        <v>-28.125</v>
+        <v>-26.5625</v>
       </c>
       <c r="C103">
-        <v>-3.6740000000000002E-2</v>
+        <v>-3.4819999999999997E-2</v>
       </c>
       <c r="D103">
-        <v>-28.125</v>
-      </c>
-      <c r="E103">
-        <v>-3.6729999999999999E-2</v>
+        <v>-26.5625</v>
+      </c>
+      <c r="E103" s="1">
+        <v>-1.11676E-5</v>
       </c>
       <c r="F103">
-        <v>-28.125</v>
+        <v>-26.5625</v>
       </c>
       <c r="G103">
-        <v>-3.6609999999999997E-2</v>
+        <v>0</v>
       </c>
       <c r="H103">
-        <v>-28.125</v>
+        <v>-26.5625</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104">
-        <v>-3.8809999999999997E-2</v>
+        <v>-3.6920000000000001E-2</v>
       </c>
       <c r="B104">
-        <v>-29.6875</v>
+        <v>-28.125</v>
       </c>
       <c r="C104">
-        <v>-3.8809999999999997E-2</v>
+        <v>-3.6859999999999997E-2</v>
       </c>
       <c r="D104">
-        <v>-29.6875</v>
-      </c>
-      <c r="E104">
-        <v>-3.8800000000000001E-2</v>
+        <v>-28.125</v>
+      </c>
+      <c r="E104" s="1">
+        <v>-5.5837900000000003E-5</v>
       </c>
       <c r="F104">
-        <v>-29.6875</v>
+        <v>-28.125</v>
       </c>
       <c r="G104">
-        <v>-3.866E-2</v>
+        <v>0</v>
       </c>
       <c r="H104">
-        <v>-29.6875</v>
+        <v>-28.125</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105">
-        <v>-4.086E-2</v>
+        <v>-3.8969999999999998E-2</v>
       </c>
       <c r="B105">
-        <v>-31.25</v>
+        <v>-29.6875</v>
       </c>
       <c r="C105">
-        <v>-4.086E-2</v>
+        <v>-3.8920000000000003E-2</v>
       </c>
       <c r="D105">
-        <v>-31.25</v>
+        <v>-29.6875</v>
       </c>
       <c r="E105">
-        <v>-4.0840000000000001E-2</v>
+        <v>-1.993E-2</v>
       </c>
       <c r="F105">
-        <v>-31.25</v>
+        <v>-29.6875</v>
       </c>
       <c r="G105">
-        <v>-4.0710000000000003E-2</v>
+        <v>0</v>
       </c>
       <c r="H105">
-        <v>-31.25</v>
+        <v>-29.6875</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106">
-        <v>-4.292E-2</v>
+        <v>-4.1020000000000001E-2</v>
       </c>
       <c r="B106">
-        <v>-32.8125</v>
+        <v>-31.25</v>
       </c>
       <c r="C106">
-        <v>-4.292E-2</v>
+        <v>-4.0969999999999999E-2</v>
       </c>
       <c r="D106">
-        <v>-32.8125</v>
+        <v>-31.25</v>
       </c>
       <c r="E106">
-        <v>-4.2889999999999998E-2</v>
+        <v>-4.1099999999999998E-2</v>
       </c>
       <c r="F106">
-        <v>-32.8125</v>
+        <v>-31.25</v>
       </c>
       <c r="G106">
-        <v>-4.2750000000000003E-2</v>
+        <v>0</v>
       </c>
       <c r="H106">
-        <v>-32.8125</v>
+        <v>-31.25</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107">
-        <v>-4.496E-2</v>
+        <v>-4.3060000000000001E-2</v>
       </c>
       <c r="B107">
-        <v>-34.375</v>
+        <v>-32.8125</v>
       </c>
       <c r="C107">
-        <v>-4.496E-2</v>
+        <v>-4.3020000000000003E-2</v>
       </c>
       <c r="D107">
-        <v>-34.375</v>
+        <v>-32.8125</v>
       </c>
       <c r="E107">
-        <v>-4.4949999999999997E-2</v>
+        <v>-4.3150000000000001E-2</v>
       </c>
       <c r="F107">
-        <v>-34.375</v>
+        <v>-32.8125</v>
       </c>
       <c r="G107">
-        <v>-4.4790000000000003E-2</v>
+        <v>0</v>
       </c>
       <c r="H107">
-        <v>-34.375</v>
+        <v>-32.8125</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108">
-        <v>-4.7030000000000002E-2</v>
+        <v>-4.5109999999999997E-2</v>
       </c>
       <c r="B108">
-        <v>-35.9375</v>
+        <v>-34.375</v>
       </c>
       <c r="C108">
-        <v>-4.7030000000000002E-2</v>
+        <v>-4.505E-2</v>
       </c>
       <c r="D108">
-        <v>-35.9375</v>
+        <v>-34.375</v>
       </c>
       <c r="E108">
-        <v>-4.7019999999999999E-2</v>
+        <v>-4.5199999999999997E-2</v>
       </c>
       <c r="F108">
-        <v>-35.9375</v>
+        <v>-34.375</v>
       </c>
       <c r="G108">
-        <v>-4.6850000000000003E-2</v>
+        <v>0</v>
       </c>
       <c r="H108">
-        <v>-35.9375</v>
+        <v>-34.375</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109">
-        <v>-4.9070000000000003E-2</v>
+        <v>-4.7169999999999997E-2</v>
       </c>
       <c r="B109">
-        <v>-37.5</v>
+        <v>-35.9375</v>
       </c>
       <c r="C109">
-        <v>-4.9070000000000003E-2</v>
+        <v>-4.7100000000000003E-2</v>
       </c>
       <c r="D109">
-        <v>-37.5</v>
+        <v>-35.9375</v>
       </c>
       <c r="E109">
-        <v>-4.9059999999999999E-2</v>
+        <v>-4.7260000000000003E-2</v>
       </c>
       <c r="F109">
-        <v>-37.5</v>
+        <v>-35.9375</v>
       </c>
       <c r="G109">
-        <v>-4.8890000000000003E-2</v>
+        <v>0</v>
       </c>
       <c r="H109">
-        <v>-37.5</v>
+        <v>-35.9375</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110">
-        <v>-5.1150000000000001E-2</v>
+        <v>-4.922E-2</v>
       </c>
       <c r="B110">
-        <v>-39.0625</v>
+        <v>-37.5</v>
       </c>
       <c r="C110">
-        <v>-5.1150000000000001E-2</v>
+        <v>-4.9149999999999999E-2</v>
       </c>
       <c r="D110">
-        <v>-39.0625</v>
+        <v>-37.5</v>
       </c>
       <c r="E110">
-        <v>-5.1139999999999998E-2</v>
+        <v>-4.9299999999999997E-2</v>
       </c>
       <c r="F110">
-        <v>-39.0625</v>
+        <v>-37.5</v>
       </c>
       <c r="G110">
-        <v>-5.0950000000000002E-2</v>
+        <v>-3.1179999999999999E-2</v>
       </c>
       <c r="H110">
-        <v>-39.0625</v>
+        <v>-37.5</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111">
-        <v>-5.3199999999999997E-2</v>
+        <v>-5.1279999999999999E-2</v>
       </c>
       <c r="B111">
-        <v>-40.625</v>
+        <v>-39.0625</v>
       </c>
       <c r="C111">
-        <v>-5.3199999999999997E-2</v>
+        <v>-5.1209999999999999E-2</v>
       </c>
       <c r="D111">
-        <v>-40.625</v>
+        <v>-39.0625</v>
       </c>
       <c r="E111">
-        <v>-5.3190000000000001E-2</v>
+        <v>-5.1369999999999999E-2</v>
       </c>
       <c r="F111">
-        <v>-40.625</v>
+        <v>-39.0625</v>
       </c>
       <c r="G111">
-        <v>-5.2979999999999999E-2</v>
+        <v>-5.1189999999999999E-2</v>
       </c>
       <c r="H111">
-        <v>-40.625</v>
+        <v>-39.0625</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112">
-        <v>-5.5259999999999997E-2</v>
+        <v>-5.3330000000000002E-2</v>
       </c>
       <c r="B112">
-        <v>-42.1875</v>
+        <v>-40.625</v>
       </c>
       <c r="C112">
-        <v>-5.527E-2</v>
+        <v>-5.3260000000000002E-2</v>
       </c>
       <c r="D112">
-        <v>-42.1875</v>
+        <v>-40.625</v>
       </c>
       <c r="E112">
-        <v>-5.525E-2</v>
+        <v>-5.3429999999999998E-2</v>
       </c>
       <c r="F112">
-        <v>-42.1875</v>
+        <v>-40.625</v>
       </c>
       <c r="G112">
-        <v>-5.5030000000000003E-2</v>
+        <v>-5.3249999999999999E-2</v>
       </c>
       <c r="H112">
-        <v>-42.1875</v>
+        <v>-40.625</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113">
-        <v>-5.731E-2</v>
+        <v>-5.5379999999999999E-2</v>
       </c>
       <c r="B113">
-        <v>-43.75</v>
+        <v>-42.1875</v>
       </c>
       <c r="C113">
-        <v>-5.731E-2</v>
+        <v>-5.5300000000000002E-2</v>
       </c>
       <c r="D113">
-        <v>-43.75</v>
+        <v>-42.1875</v>
       </c>
       <c r="E113">
-        <v>-5.7290000000000001E-2</v>
+        <v>-5.5480000000000002E-2</v>
       </c>
       <c r="F113">
-        <v>-43.75</v>
+        <v>-42.1875</v>
       </c>
       <c r="G113">
-        <v>-5.7079999999999999E-2</v>
+        <v>-5.5289999999999999E-2</v>
       </c>
       <c r="H113">
-        <v>-43.75</v>
+        <v>-42.1875</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114">
-        <v>-5.9369999999999999E-2</v>
+        <v>-5.7419999999999999E-2</v>
       </c>
       <c r="B114">
-        <v>-45.3125</v>
+        <v>-43.75</v>
       </c>
       <c r="C114">
-        <v>-5.9380000000000002E-2</v>
+        <v>-5.7349999999999998E-2</v>
       </c>
       <c r="D114">
-        <v>-45.3125</v>
+        <v>-43.75</v>
       </c>
       <c r="E114">
-        <v>-5.9339999999999997E-2</v>
+        <v>-5.7540000000000001E-2</v>
       </c>
       <c r="F114">
-        <v>-45.3125</v>
+        <v>-43.75</v>
       </c>
       <c r="G114">
-        <v>-5.9119999999999999E-2</v>
+        <v>-5.7329999999999999E-2</v>
       </c>
       <c r="H114">
-        <v>-45.3125</v>
+        <v>-43.75</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115">
-        <v>-6.1420000000000002E-2</v>
+        <v>-5.9479999999999998E-2</v>
       </c>
       <c r="B115">
-        <v>-46.875</v>
+        <v>-45.3125</v>
       </c>
       <c r="C115">
-        <v>-6.1429999999999998E-2</v>
+        <v>-5.9400000000000001E-2</v>
       </c>
       <c r="D115">
-        <v>-46.875</v>
+        <v>-45.3125</v>
       </c>
       <c r="E115">
-        <v>-6.1400000000000003E-2</v>
+        <v>-5.9580000000000001E-2</v>
       </c>
       <c r="F115">
-        <v>-46.875</v>
+        <v>-45.3125</v>
       </c>
       <c r="G115">
-        <v>-6.1159999999999999E-2</v>
+        <v>-5.9380000000000002E-2</v>
       </c>
       <c r="H115">
-        <v>-46.875</v>
+        <v>-45.3125</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116">
-        <v>-6.3490000000000005E-2</v>
+        <v>-6.1519999999999998E-2</v>
       </c>
       <c r="B116">
-        <v>-48.4375</v>
+        <v>-46.875</v>
       </c>
       <c r="C116">
-        <v>-6.3500000000000001E-2</v>
+        <v>-6.1429999999999998E-2</v>
       </c>
       <c r="D116">
-        <v>-48.4375</v>
+        <v>-46.875</v>
       </c>
       <c r="E116">
-        <v>-6.3469999999999999E-2</v>
+        <v>-6.1629999999999997E-2</v>
       </c>
       <c r="F116">
-        <v>-48.4375</v>
+        <v>-46.875</v>
       </c>
       <c r="G116">
-        <v>-6.3219999999999998E-2</v>
+        <v>-6.1420000000000002E-2</v>
       </c>
       <c r="H116">
-        <v>-48.4375</v>
+        <v>-46.875</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117">
-        <v>-6.5540000000000001E-2</v>
+        <v>-6.3579999999999998E-2</v>
       </c>
       <c r="B117">
-        <v>-50</v>
+        <v>-48.4375</v>
       </c>
       <c r="C117">
-        <v>-6.5549999999999997E-2</v>
+        <v>-6.3500000000000001E-2</v>
       </c>
       <c r="D117">
-        <v>-50</v>
+        <v>-48.4375</v>
       </c>
       <c r="E117">
-        <v>-6.5519999999999995E-2</v>
+        <v>-6.3700000000000007E-2</v>
       </c>
       <c r="F117">
-        <v>-50</v>
+        <v>-48.4375</v>
       </c>
       <c r="G117">
-        <v>-6.5259999999999999E-2</v>
+        <v>-6.3479999999999995E-2</v>
       </c>
       <c r="H117">
-        <v>-50</v>
+        <v>-48.4375</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118">
-        <v>-6.7680000000000004E-2</v>
+        <v>-6.5629999999999994E-2</v>
       </c>
       <c r="B118">
-        <v>-51.5625</v>
+        <v>-50</v>
       </c>
       <c r="C118">
-        <v>-6.7680000000000004E-2</v>
+        <v>-6.5540000000000001E-2</v>
       </c>
       <c r="D118">
-        <v>-51.5625</v>
+        <v>-50</v>
       </c>
       <c r="E118">
-        <v>-6.7640000000000006E-2</v>
+        <v>-6.5750000000000003E-2</v>
       </c>
       <c r="F118">
-        <v>-51.5625</v>
+        <v>-50</v>
       </c>
       <c r="G118">
-        <v>-6.7369999999999999E-2</v>
+        <v>-6.5519999999999995E-2</v>
       </c>
       <c r="H118">
-        <v>-51.5625</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119">
-        <v>-6.973E-2</v>
+        <v>-6.7750000000000005E-2</v>
       </c>
       <c r="B119">
-        <v>-53.125</v>
+        <v>-51.5625</v>
       </c>
       <c r="C119">
-        <v>-6.973E-2</v>
+        <v>-6.7650000000000002E-2</v>
       </c>
       <c r="D119">
-        <v>-53.125</v>
+        <v>-51.5625</v>
       </c>
       <c r="E119">
-        <v>-6.9699999999999998E-2</v>
+        <v>-6.787E-2</v>
       </c>
       <c r="F119">
-        <v>-53.125</v>
+        <v>-51.5625</v>
       </c>
       <c r="G119">
-        <v>-6.9409999999999999E-2</v>
+        <v>-6.7629999999999996E-2</v>
       </c>
       <c r="H119">
-        <v>-53.125</v>
+        <v>-51.5625</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120">
-        <v>-7.1800000000000003E-2</v>
+        <v>-6.9800000000000001E-2</v>
       </c>
       <c r="B120">
-        <v>-54.6875</v>
+        <v>-53.125</v>
       </c>
       <c r="C120">
-        <v>-7.1790000000000007E-2</v>
+        <v>-6.9709999999999994E-2</v>
       </c>
       <c r="D120">
-        <v>-54.6875</v>
+        <v>-53.125</v>
       </c>
       <c r="E120">
-        <v>-7.1749999999999994E-2</v>
+        <v>-6.9919999999999996E-2</v>
       </c>
       <c r="F120">
-        <v>-54.6875</v>
+        <v>-53.125</v>
       </c>
       <c r="G120">
-        <v>-7.1470000000000006E-2</v>
+        <v>-6.9669999999999996E-2</v>
       </c>
       <c r="H120">
-        <v>-54.6875</v>
+        <v>-53.125</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121">
-        <v>-7.3859999999999995E-2</v>
+        <v>-7.1859999999999993E-2</v>
       </c>
       <c r="B121">
-        <v>-56.25</v>
+        <v>-54.6875</v>
       </c>
       <c r="C121">
-        <v>-7.3840000000000003E-2</v>
+        <v>-7.1760000000000004E-2</v>
       </c>
       <c r="D121">
-        <v>-56.25</v>
+        <v>-54.6875</v>
       </c>
       <c r="E121">
-        <v>-7.3810000000000001E-2</v>
+        <v>-7.1989999999999998E-2</v>
       </c>
       <c r="F121">
-        <v>-56.25</v>
+        <v>-54.6875</v>
       </c>
       <c r="G121">
-        <v>-7.3520000000000002E-2</v>
+        <v>-7.1730000000000002E-2</v>
       </c>
       <c r="H121">
-        <v>-56.25</v>
+        <v>-54.6875</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122">
-        <v>-7.5920000000000001E-2</v>
+        <v>-7.3910000000000003E-2</v>
       </c>
       <c r="B122">
-        <v>-57.8125</v>
+        <v>-56.25</v>
       </c>
       <c r="C122">
-        <v>-7.5910000000000005E-2</v>
+        <v>-7.3810000000000001E-2</v>
       </c>
       <c r="D122">
-        <v>-57.8125</v>
+        <v>-56.25</v>
       </c>
       <c r="E122">
-        <v>-7.5870000000000007E-2</v>
+        <v>-7.4039999999999995E-2</v>
       </c>
       <c r="F122">
-        <v>-57.8125</v>
+        <v>-56.25</v>
       </c>
       <c r="G122">
-        <v>-7.5560000000000002E-2</v>
+        <v>-7.3770000000000002E-2</v>
       </c>
       <c r="H122">
-        <v>-57.8125</v>
+        <v>-56.25</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123">
-        <v>-7.7979999999999994E-2</v>
+        <v>-7.596E-2</v>
       </c>
       <c r="B123">
-        <v>-59.375</v>
+        <v>-57.8125</v>
       </c>
       <c r="C123">
-        <v>-7.7960000000000002E-2</v>
+        <v>-7.5859999999999997E-2</v>
       </c>
       <c r="D123">
-        <v>-59.375</v>
+        <v>-57.8125</v>
       </c>
       <c r="E123">
-        <v>-7.7939999999999995E-2</v>
+        <v>-7.6100000000000001E-2</v>
       </c>
       <c r="F123">
-        <v>-59.375</v>
+        <v>-57.8125</v>
       </c>
       <c r="G123">
-        <v>-7.7609999999999998E-2</v>
+        <v>-7.5829999999999995E-2</v>
       </c>
       <c r="H123">
-        <v>-59.375</v>
+        <v>-57.8125</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124">
-        <v>-8.0049999999999996E-2</v>
+        <v>-7.8020000000000006E-2</v>
       </c>
       <c r="B124">
-        <v>-60.9375</v>
+        <v>-59.375</v>
       </c>
       <c r="C124">
-        <v>-8.0019999999999994E-2</v>
+        <v>-7.7920000000000003E-2</v>
       </c>
       <c r="D124">
-        <v>-60.9375</v>
+        <v>-59.375</v>
       </c>
       <c r="E124">
-        <v>-0.08</v>
+        <v>-7.8149999999999997E-2</v>
       </c>
       <c r="F124">
-        <v>-60.9375</v>
+        <v>-59.375</v>
       </c>
       <c r="G124">
-        <v>-7.9680000000000001E-2</v>
+        <v>-7.7869999999999995E-2</v>
       </c>
       <c r="H124">
-        <v>-60.9375</v>
+        <v>-59.375</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125">
-        <v>-7.8229999999999994E-2</v>
+        <v>-8.0089999999999995E-2</v>
       </c>
       <c r="B125">
-        <v>-59.375</v>
+        <v>-60.9375</v>
       </c>
       <c r="C125">
-        <v>-7.8210000000000002E-2</v>
+        <v>-7.9979999999999996E-2</v>
       </c>
       <c r="D125">
-        <v>-59.375</v>
+        <v>-60.9375</v>
       </c>
       <c r="E125">
-        <v>-7.8149999999999997E-2</v>
+        <v>-8.022E-2</v>
       </c>
       <c r="F125">
-        <v>-59.375</v>
+        <v>-60.9375</v>
       </c>
       <c r="G125">
         <v>-7.9930000000000001E-2</v>
@@ -3511,997 +3511,1023 @@
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126">
-        <v>-7.6160000000000005E-2</v>
+        <v>-7.9880000000000007E-2</v>
       </c>
       <c r="B126">
-        <v>-57.8125</v>
+        <v>-60.9375</v>
       </c>
       <c r="C126">
-        <v>-7.6149999999999995E-2</v>
+        <v>-7.9810000000000006E-2</v>
       </c>
       <c r="D126">
-        <v>-57.8125</v>
+        <v>-60.9375</v>
       </c>
       <c r="E126">
-        <v>-7.6100000000000001E-2</v>
+        <v>-0.08</v>
       </c>
       <c r="F126">
-        <v>-57.8125</v>
+        <v>-60.9375</v>
       </c>
       <c r="G126">
-        <v>-7.7869999999999995E-2</v>
+        <v>-7.9680000000000001E-2</v>
       </c>
       <c r="H126">
-        <v>-59.375</v>
+        <v>-60.9375</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127">
-        <v>-7.4109999999999995E-2</v>
+        <v>-7.782E-2</v>
       </c>
       <c r="B127">
-        <v>-56.25</v>
+        <v>-59.375</v>
       </c>
       <c r="C127">
-        <v>-7.4090000000000003E-2</v>
+        <v>-7.7759999999999996E-2</v>
       </c>
       <c r="D127">
-        <v>-56.25</v>
+        <v>-59.375</v>
       </c>
       <c r="E127">
-        <v>-7.4039999999999995E-2</v>
+        <v>-7.7939999999999995E-2</v>
       </c>
       <c r="F127">
-        <v>-56.25</v>
+        <v>-59.375</v>
       </c>
       <c r="G127">
-        <v>-7.5829999999999995E-2</v>
+        <v>-7.7609999999999998E-2</v>
       </c>
       <c r="H127">
-        <v>-57.8125</v>
+        <v>-59.375</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128">
-        <v>-7.2050000000000003E-2</v>
+        <v>-7.5759999999999994E-2</v>
       </c>
       <c r="B128">
-        <v>-54.6875</v>
+        <v>-57.8125</v>
       </c>
       <c r="C128">
-        <v>-7.2029999999999997E-2</v>
+        <v>-7.571E-2</v>
       </c>
       <c r="D128">
-        <v>-54.6875</v>
+        <v>-57.8125</v>
       </c>
       <c r="E128">
-        <v>-7.1989999999999998E-2</v>
+        <v>-7.5870000000000007E-2</v>
       </c>
       <c r="F128">
-        <v>-54.6875</v>
+        <v>-57.8125</v>
       </c>
       <c r="G128">
-        <v>-7.3770000000000002E-2</v>
+        <v>-7.5560000000000002E-2</v>
       </c>
       <c r="H128">
-        <v>-56.25</v>
+        <v>-57.8125</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129">
-        <v>-6.9989999999999997E-2</v>
+        <v>-7.3709999999999998E-2</v>
       </c>
       <c r="B129">
-        <v>-53.125</v>
+        <v>-56.25</v>
       </c>
       <c r="C129">
-        <v>-6.9959999999999994E-2</v>
+        <v>-7.3649999999999993E-2</v>
       </c>
       <c r="D129">
-        <v>-53.125</v>
+        <v>-56.25</v>
       </c>
       <c r="E129">
-        <v>-6.9919999999999996E-2</v>
+        <v>-7.3810000000000001E-2</v>
       </c>
       <c r="F129">
-        <v>-53.125</v>
+        <v>-56.25</v>
       </c>
       <c r="G129">
-        <v>-7.1730000000000002E-2</v>
+        <v>-7.3520000000000002E-2</v>
       </c>
       <c r="H129">
-        <v>-54.6875</v>
+        <v>-56.25</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130">
-        <v>-6.7930000000000004E-2</v>
+        <v>-7.1650000000000005E-2</v>
       </c>
       <c r="B130">
-        <v>-51.5625</v>
+        <v>-54.6875</v>
       </c>
       <c r="C130">
-        <v>-6.7909999999999998E-2</v>
+        <v>-7.1580000000000005E-2</v>
       </c>
       <c r="D130">
-        <v>-51.5625</v>
+        <v>-54.6875</v>
       </c>
       <c r="E130">
-        <v>-6.787E-2</v>
+        <v>-7.1749999999999994E-2</v>
       </c>
       <c r="F130">
-        <v>-51.5625</v>
+        <v>-54.6875</v>
       </c>
       <c r="G130">
-        <v>-6.9669999999999996E-2</v>
+        <v>-7.1470000000000006E-2</v>
       </c>
       <c r="H130">
-        <v>-53.125</v>
+        <v>-54.6875</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131">
-        <v>-6.5809999999999994E-2</v>
+        <v>-6.9589999999999999E-2</v>
       </c>
       <c r="B131">
-        <v>-50</v>
+        <v>-53.125</v>
       </c>
       <c r="C131">
-        <v>-6.5799999999999997E-2</v>
+        <v>-6.9529999999999995E-2</v>
       </c>
       <c r="D131">
-        <v>-50</v>
+        <v>-53.125</v>
       </c>
       <c r="E131">
-        <v>-6.5750000000000003E-2</v>
+        <v>-6.9699999999999998E-2</v>
       </c>
       <c r="F131">
-        <v>-50</v>
+        <v>-53.125</v>
       </c>
       <c r="G131">
-        <v>-6.7629999999999996E-2</v>
+        <v>-6.9409999999999999E-2</v>
       </c>
       <c r="H131">
-        <v>-51.5625</v>
+        <v>-53.125</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132">
-        <v>-6.3759999999999997E-2</v>
+        <v>-6.7540000000000003E-2</v>
       </c>
       <c r="B132">
-        <v>-48.4375</v>
+        <v>-51.5625</v>
       </c>
       <c r="C132">
-        <v>-6.3740000000000005E-2</v>
+        <v>-6.7470000000000002E-2</v>
       </c>
       <c r="D132">
-        <v>-48.4375</v>
+        <v>-51.5625</v>
       </c>
       <c r="E132">
-        <v>-6.3700000000000007E-2</v>
+        <v>-6.7640000000000006E-2</v>
       </c>
       <c r="F132">
-        <v>-48.4375</v>
+        <v>-51.5625</v>
       </c>
       <c r="G132">
-        <v>-6.5519999999999995E-2</v>
+        <v>-6.7369999999999999E-2</v>
       </c>
       <c r="H132">
-        <v>-50</v>
+        <v>-51.5625</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133">
-        <v>-6.1690000000000002E-2</v>
+        <v>-6.5420000000000006E-2</v>
       </c>
       <c r="B133">
-        <v>-46.875</v>
+        <v>-50</v>
       </c>
       <c r="C133">
-        <v>-6.1679999999999999E-2</v>
+        <v>-6.5350000000000005E-2</v>
       </c>
       <c r="D133">
-        <v>-46.875</v>
+        <v>-50</v>
       </c>
       <c r="E133">
-        <v>-6.1629999999999997E-2</v>
+        <v>-6.5519999999999995E-2</v>
       </c>
       <c r="F133">
-        <v>-46.875</v>
+        <v>-50</v>
       </c>
       <c r="G133">
-        <v>-6.3479999999999995E-2</v>
+        <v>-6.5259999999999999E-2</v>
       </c>
       <c r="H133">
-        <v>-48.4375</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134">
-        <v>-5.9650000000000002E-2</v>
+        <v>-6.336E-2</v>
       </c>
       <c r="B134">
-        <v>-45.3125</v>
+        <v>-48.4375</v>
       </c>
       <c r="C134">
-        <v>-5.9619999999999999E-2</v>
+        <v>-6.3299999999999995E-2</v>
       </c>
       <c r="D134">
-        <v>-45.3125</v>
+        <v>-48.4375</v>
       </c>
       <c r="E134">
-        <v>-5.9580000000000001E-2</v>
+        <v>-6.3469999999999999E-2</v>
       </c>
       <c r="F134">
-        <v>-45.3125</v>
+        <v>-48.4375</v>
       </c>
       <c r="G134">
-        <v>-6.1420000000000002E-2</v>
+        <v>-6.3219999999999998E-2</v>
       </c>
       <c r="H134">
-        <v>-46.875</v>
+        <v>-48.4375</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135">
-        <v>-5.7590000000000002E-2</v>
+        <v>-6.13E-2</v>
       </c>
       <c r="B135">
-        <v>-43.75</v>
+        <v>-46.875</v>
       </c>
       <c r="C135">
-        <v>-5.7570000000000003E-2</v>
+        <v>-6.1240000000000003E-2</v>
       </c>
       <c r="D135">
-        <v>-43.75</v>
+        <v>-46.875</v>
       </c>
       <c r="E135">
-        <v>-5.7540000000000001E-2</v>
+        <v>-6.1400000000000003E-2</v>
       </c>
       <c r="F135">
-        <v>-43.75</v>
+        <v>-46.875</v>
       </c>
       <c r="G135">
-        <v>-5.9380000000000002E-2</v>
+        <v>-6.1159999999999999E-2</v>
       </c>
       <c r="H135">
-        <v>-45.3125</v>
+        <v>-46.875</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136">
-        <v>-5.5539999999999999E-2</v>
+        <v>-5.926E-2</v>
       </c>
       <c r="B136">
-        <v>-42.1875</v>
+        <v>-45.3125</v>
       </c>
       <c r="C136">
-        <v>-5.5530000000000003E-2</v>
+        <v>-5.919E-2</v>
       </c>
       <c r="D136">
-        <v>-42.1875</v>
+        <v>-45.3125</v>
       </c>
       <c r="E136">
-        <v>-5.5480000000000002E-2</v>
+        <v>-5.9339999999999997E-2</v>
       </c>
       <c r="F136">
-        <v>-42.1875</v>
+        <v>-45.3125</v>
       </c>
       <c r="G136">
-        <v>-5.7329999999999999E-2</v>
+        <v>-5.9110000000000003E-2</v>
       </c>
       <c r="H136">
-        <v>-43.75</v>
+        <v>-45.3125</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137">
-        <v>-5.348E-2</v>
+        <v>-5.7200000000000001E-2</v>
       </c>
       <c r="B137">
-        <v>-40.625</v>
+        <v>-43.75</v>
       </c>
       <c r="C137">
-        <v>-5.3460000000000001E-2</v>
+        <v>-5.713E-2</v>
       </c>
       <c r="D137">
-        <v>-40.625</v>
+        <v>-43.75</v>
       </c>
       <c r="E137">
-        <v>-5.3429999999999998E-2</v>
+        <v>-5.7290000000000001E-2</v>
       </c>
       <c r="F137">
-        <v>-40.625</v>
+        <v>-43.75</v>
       </c>
       <c r="G137">
-        <v>-5.5289999999999999E-2</v>
+        <v>-5.7079999999999999E-2</v>
       </c>
       <c r="H137">
-        <v>-42.1875</v>
+        <v>-43.75</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138">
-        <v>-5.1429999999999997E-2</v>
+        <v>-5.5149999999999998E-2</v>
       </c>
       <c r="B138">
-        <v>-39.0625</v>
+        <v>-42.1875</v>
       </c>
       <c r="C138">
-        <v>-5.142E-2</v>
+        <v>-5.509E-2</v>
       </c>
       <c r="D138">
-        <v>-39.0625</v>
+        <v>-42.1875</v>
       </c>
       <c r="E138">
-        <v>-5.1369999999999999E-2</v>
+        <v>-5.525E-2</v>
       </c>
       <c r="F138">
-        <v>-39.0625</v>
+        <v>-42.1875</v>
       </c>
       <c r="G138">
-        <v>-5.3249999999999999E-2</v>
+        <v>-5.5019999999999999E-2</v>
       </c>
       <c r="H138">
-        <v>-40.625</v>
+        <v>-42.1875</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139">
-        <v>-4.9360000000000001E-2</v>
+        <v>-5.3089999999999998E-2</v>
       </c>
       <c r="B139">
-        <v>-37.5</v>
+        <v>-40.625</v>
       </c>
       <c r="C139">
-        <v>-4.9340000000000002E-2</v>
+        <v>-5.3019999999999998E-2</v>
       </c>
       <c r="D139">
-        <v>-37.5</v>
+        <v>-40.625</v>
       </c>
       <c r="E139">
-        <v>-4.9299999999999997E-2</v>
+        <v>-5.3190000000000001E-2</v>
       </c>
       <c r="F139">
-        <v>-37.5</v>
+        <v>-40.625</v>
       </c>
       <c r="G139">
-        <v>-5.1189999999999999E-2</v>
+        <v>-5.2979999999999999E-2</v>
       </c>
       <c r="H139">
-        <v>-39.0625</v>
+        <v>-40.625</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140">
-        <v>-4.7309999999999998E-2</v>
+        <v>-5.1049999999999998E-2</v>
       </c>
       <c r="B140">
-        <v>-35.9375</v>
+        <v>-39.0625</v>
       </c>
       <c r="C140">
-        <v>-4.7289999999999999E-2</v>
+        <v>-5.0979999999999998E-2</v>
       </c>
       <c r="D140">
-        <v>-35.9375</v>
+        <v>-39.0625</v>
       </c>
       <c r="E140">
-        <v>-4.7260000000000003E-2</v>
+        <v>-5.1139999999999998E-2</v>
       </c>
       <c r="F140">
-        <v>-35.9375</v>
+        <v>-39.0625</v>
       </c>
       <c r="G140">
-        <v>-3.1179999999999999E-2</v>
+        <v>-5.0950000000000002E-2</v>
       </c>
       <c r="H140">
-        <v>-37.5</v>
+        <v>-39.0625</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141">
-        <v>-4.5240000000000002E-2</v>
+        <v>-4.897E-2</v>
       </c>
       <c r="B141">
-        <v>-34.375</v>
+        <v>-37.5</v>
       </c>
       <c r="C141">
-        <v>-4.5229999999999999E-2</v>
+        <v>-4.8899999999999999E-2</v>
       </c>
       <c r="D141">
-        <v>-34.375</v>
+        <v>-37.5</v>
       </c>
       <c r="E141">
-        <v>-4.5199999999999997E-2</v>
+        <v>-4.9059999999999999E-2</v>
       </c>
       <c r="F141">
-        <v>-34.375</v>
+        <v>-37.5</v>
       </c>
       <c r="G141">
-        <v>0</v>
+        <v>-4.8890000000000003E-2</v>
       </c>
       <c r="H141">
-        <v>-35.9375</v>
+        <v>-37.5</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142">
-        <v>-4.3200000000000002E-2</v>
+        <v>-4.6929999999999999E-2</v>
       </c>
       <c r="B142">
-        <v>-32.8125</v>
+        <v>-35.9375</v>
       </c>
       <c r="C142">
-        <v>-4.317E-2</v>
+        <v>-4.6859999999999999E-2</v>
       </c>
       <c r="D142">
-        <v>-32.8125</v>
+        <v>-35.9375</v>
       </c>
       <c r="E142">
-        <v>-4.3150000000000001E-2</v>
+        <v>-4.7019999999999999E-2</v>
       </c>
       <c r="F142">
-        <v>-32.8125</v>
+        <v>-35.9375</v>
       </c>
       <c r="G142">
-        <v>0</v>
+        <v>-4.6850000000000003E-2</v>
       </c>
       <c r="H142">
-        <v>-34.375</v>
+        <v>-35.9375</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143">
-        <v>-4.1140000000000003E-2</v>
+        <v>-4.487E-2</v>
       </c>
       <c r="B143">
-        <v>-31.25</v>
+        <v>-34.375</v>
       </c>
       <c r="C143">
-        <v>-4.1119999999999997E-2</v>
+        <v>-4.48E-2</v>
       </c>
       <c r="D143">
-        <v>-31.25</v>
+        <v>-34.375</v>
       </c>
       <c r="E143">
-        <v>-4.1099999999999998E-2</v>
+        <v>-4.4949999999999997E-2</v>
       </c>
       <c r="F143">
-        <v>-31.25</v>
+        <v>-34.375</v>
       </c>
       <c r="G143">
-        <v>0</v>
+        <v>-4.4790000000000003E-2</v>
       </c>
       <c r="H143">
-        <v>-32.8125</v>
+        <v>-34.375</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144">
-        <v>-3.909E-2</v>
+        <v>-4.2819999999999997E-2</v>
       </c>
       <c r="B144">
-        <v>-29.6875</v>
+        <v>-32.8125</v>
       </c>
       <c r="C144">
-        <v>-3.9079999999999997E-2</v>
+        <v>-4.2759999999999999E-2</v>
       </c>
       <c r="D144">
-        <v>-29.6875</v>
+        <v>-32.8125</v>
       </c>
       <c r="E144">
-        <v>-1.993E-2</v>
+        <v>-4.2889999999999998E-2</v>
       </c>
       <c r="F144">
-        <v>-29.6875</v>
+        <v>-32.8125</v>
       </c>
       <c r="G144">
-        <v>0</v>
+        <v>-4.2750000000000003E-2</v>
       </c>
       <c r="H144">
-        <v>-31.25</v>
+        <v>-32.8125</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145">
-        <v>-3.7019999999999997E-2</v>
+        <v>-4.0770000000000001E-2</v>
       </c>
       <c r="B145">
-        <v>-28.125</v>
+        <v>-31.25</v>
       </c>
       <c r="C145">
-        <v>-3.7010000000000001E-2</v>
+        <v>-4.0719999999999999E-2</v>
       </c>
       <c r="D145">
-        <v>-28.125</v>
+        <v>-31.25</v>
       </c>
       <c r="E145" s="1">
-        <v>-5.5837900000000003E-5</v>
+        <v>-4.0840000000000001E-2</v>
       </c>
       <c r="F145">
-        <v>-28.125</v>
+        <v>-31.25</v>
       </c>
       <c r="G145">
-        <v>0</v>
+        <v>-4.0719999999999999E-2</v>
       </c>
       <c r="H145">
-        <v>-29.6875</v>
+        <v>-31.25</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146">
-        <v>-3.4970000000000001E-2</v>
+        <v>-3.8730000000000001E-2</v>
       </c>
       <c r="B146">
-        <v>-26.5625</v>
+        <v>-29.6875</v>
       </c>
       <c r="C146">
-        <v>-3.4950000000000002E-2</v>
+        <v>-3.8670000000000003E-2</v>
       </c>
       <c r="D146">
-        <v>-26.5625</v>
+        <v>-29.6875</v>
       </c>
       <c r="E146" s="1">
-        <v>-1.11676E-5</v>
+        <v>-3.8800000000000001E-2</v>
       </c>
       <c r="F146">
-        <v>-26.5625</v>
+        <v>-29.6875</v>
       </c>
       <c r="G146">
-        <v>0</v>
+        <v>-3.866E-2</v>
       </c>
       <c r="H146">
-        <v>-28.125</v>
+        <v>-29.6875</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147">
-        <v>-3.2919999999999998E-2</v>
+        <v>-3.6659999999999998E-2</v>
       </c>
       <c r="B147">
-        <v>-25</v>
+        <v>-28.125</v>
       </c>
       <c r="C147">
-        <v>-3.2899999999999999E-2</v>
+        <v>-3.6609999999999997E-2</v>
       </c>
       <c r="D147">
-        <v>-25</v>
+        <v>-28.125</v>
       </c>
       <c r="E147">
-        <v>0</v>
+        <v>-3.6729999999999999E-2</v>
       </c>
       <c r="F147">
-        <v>-25</v>
+        <v>-28.125</v>
       </c>
       <c r="G147">
-        <v>0</v>
+        <v>-3.6609999999999997E-2</v>
       </c>
       <c r="H147">
-        <v>-26.5625</v>
+        <v>-28.125</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A148">
-        <v>-3.0880000000000001E-2</v>
+        <v>-3.4619999999999998E-2</v>
       </c>
       <c r="B148">
-        <v>-23.4375</v>
+        <v>-26.5625</v>
       </c>
       <c r="C148">
-        <v>-3.0859999999999999E-2</v>
+        <v>-3.4569999999999997E-2</v>
       </c>
       <c r="D148">
-        <v>-23.4375</v>
+        <v>-26.5625</v>
       </c>
       <c r="E148">
-        <v>0</v>
+        <v>-3.4680000000000002E-2</v>
       </c>
       <c r="F148">
-        <v>-23.4375</v>
+        <v>-26.5625</v>
       </c>
       <c r="G148">
-        <v>0</v>
+        <v>-3.456E-2</v>
       </c>
       <c r="H148">
-        <v>-25</v>
+        <v>-26.5625</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A149">
-        <v>-2.8809999999999999E-2</v>
+        <v>-3.2579999999999998E-2</v>
       </c>
       <c r="B149">
-        <v>-21.875</v>
+        <v>-25</v>
       </c>
       <c r="C149">
-        <v>-2.879E-2</v>
+        <v>-3.2530000000000003E-2</v>
       </c>
       <c r="D149">
-        <v>-21.875</v>
+        <v>-25</v>
       </c>
       <c r="E149" s="1">
-        <v>1.11676E-5</v>
+        <v>-3.2620000000000003E-2</v>
       </c>
       <c r="F149">
-        <v>-21.875</v>
+        <v>-25</v>
       </c>
       <c r="G149">
-        <v>0</v>
+        <v>-3.252E-2</v>
       </c>
       <c r="H149">
-        <v>-23.4375</v>
+        <v>-25</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A150">
-        <v>-2.6759999999999999E-2</v>
+        <v>-3.0530000000000002E-2</v>
       </c>
       <c r="B150">
-        <v>-20.3125</v>
+        <v>-23.4375</v>
       </c>
       <c r="C150">
-        <v>-1.644E-2</v>
+        <v>-3.049E-2</v>
       </c>
       <c r="D150">
-        <v>-20.3125</v>
+        <v>-23.4375</v>
       </c>
       <c r="E150" s="1">
-        <v>1.11676E-5</v>
+        <v>-3.058E-2</v>
       </c>
       <c r="F150">
-        <v>-20.3125</v>
+        <v>-23.4375</v>
       </c>
       <c r="G150">
-        <v>0</v>
+        <v>-3.0470000000000001E-2</v>
       </c>
       <c r="H150">
-        <v>-21.875</v>
+        <v>-23.4375</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A151">
-        <v>-2.47E-2</v>
+        <v>-2.8479999999999998E-2</v>
       </c>
       <c r="B151">
-        <v>-18.75</v>
+        <v>-21.875</v>
       </c>
       <c r="C151" s="1">
-        <v>-2.6802199999999998E-4</v>
+        <v>-2.843E-2</v>
       </c>
       <c r="D151">
-        <v>-18.75</v>
+        <v>-21.875</v>
       </c>
       <c r="E151" s="1">
-        <v>1.11676E-5</v>
+        <v>-2.852E-2</v>
       </c>
       <c r="F151">
-        <v>-18.75</v>
+        <v>-21.875</v>
       </c>
       <c r="G151">
-        <v>0</v>
+        <v>-2.843E-2</v>
       </c>
       <c r="H151">
-        <v>-20.3125</v>
+        <v>-21.875</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A152">
-        <v>-2.265E-2</v>
+        <v>-2.6419999999999999E-2</v>
       </c>
       <c r="B152">
-        <v>-17.1875</v>
+        <v>-20.3125</v>
       </c>
       <c r="C152" s="1">
-        <v>-1.0050799999999999E-4</v>
+        <v>-2.639E-2</v>
       </c>
       <c r="D152">
-        <v>-17.1875</v>
+        <v>-20.3125</v>
       </c>
       <c r="E152" s="1">
-        <v>1.11676E-5</v>
+        <v>-2.647E-2</v>
       </c>
       <c r="F152">
-        <v>-17.1875</v>
+        <v>-20.3125</v>
       </c>
       <c r="G152">
-        <v>0</v>
+        <v>-2.6380000000000001E-2</v>
       </c>
       <c r="H152">
-        <v>-18.75</v>
+        <v>-20.3125</v>
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A153">
-        <v>-2.0580000000000001E-2</v>
+        <v>-2.4379999999999999E-2</v>
       </c>
       <c r="B153">
-        <v>-15.625</v>
+        <v>-18.75</v>
       </c>
       <c r="C153" s="1">
-        <v>-3.35028E-5</v>
+        <v>-2.435E-2</v>
       </c>
       <c r="D153">
-        <v>-15.625</v>
+        <v>-18.75</v>
       </c>
       <c r="E153" s="1">
-        <v>1.11676E-5</v>
+        <v>-2.4410000000000001E-2</v>
       </c>
       <c r="F153">
-        <v>-15.625</v>
+        <v>-18.75</v>
       </c>
       <c r="G153">
-        <v>0</v>
+        <v>-2.4330000000000001E-2</v>
       </c>
       <c r="H153">
-        <v>-17.1875</v>
+        <v>-18.75</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A154">
-        <v>-1.8530000000000001E-2</v>
+        <v>-2.2339999999999999E-2</v>
       </c>
       <c r="B154">
-        <v>-14.0625</v>
+        <v>-17.1875</v>
       </c>
       <c r="C154" s="1">
-        <v>-1.11676E-5</v>
+        <v>-2.23E-2</v>
       </c>
       <c r="D154">
-        <v>-14.0625</v>
+        <v>-17.1875</v>
       </c>
       <c r="E154" s="1">
-        <v>1.11676E-5</v>
+        <v>-2.2339999999999999E-2</v>
       </c>
       <c r="F154">
-        <v>-14.0625</v>
+        <v>-17.1875</v>
       </c>
       <c r="G154">
-        <v>0</v>
+        <v>-2.2110000000000001E-2</v>
       </c>
       <c r="H154">
-        <v>-15.625</v>
+        <v>-17.1875</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A155">
-        <v>-1.6459999999999999E-2</v>
+        <v>-2.027E-2</v>
       </c>
       <c r="B155">
-        <v>-12.5</v>
+        <v>-15.625</v>
       </c>
       <c r="C155">
-        <v>0</v>
+        <v>-2.0219999999999998E-2</v>
       </c>
       <c r="D155">
-        <v>-12.5</v>
+        <v>-15.625</v>
       </c>
       <c r="E155" s="1">
-        <v>1.11676E-5</v>
+        <v>-1.9400000000000001E-2</v>
       </c>
       <c r="F155">
-        <v>-12.5</v>
+        <v>-15.625</v>
       </c>
       <c r="G155">
-        <v>0</v>
+        <v>-7.8200000000000006E-3</v>
       </c>
       <c r="H155">
-        <v>-14.0625</v>
+        <v>-15.625</v>
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A156">
-        <v>-1.44E-2</v>
+        <v>-1.8239999999999999E-2</v>
       </c>
       <c r="B156">
-        <v>-10.9375</v>
+        <v>-14.0625</v>
       </c>
       <c r="C156">
-        <v>0</v>
+        <v>-1.7909999999999999E-2</v>
       </c>
       <c r="D156">
-        <v>-10.9375</v>
+        <v>-14.0625</v>
       </c>
       <c r="E156" s="1">
-        <v>1.11676E-5</v>
+        <v>-3.3300000000000001E-3</v>
       </c>
       <c r="F156">
-        <v>-10.9375</v>
+        <v>-14.0625</v>
       </c>
       <c r="G156">
         <v>0</v>
       </c>
       <c r="H156">
-        <v>-12.5</v>
+        <v>-14.0625</v>
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A157">
-        <v>-1.217E-2</v>
+        <v>-1.617E-2</v>
       </c>
       <c r="B157">
-        <v>-9.375</v>
+        <v>-12.5</v>
       </c>
       <c r="C157">
-        <v>0</v>
+        <v>-1.2449999999999999E-2</v>
       </c>
       <c r="D157">
-        <v>-9.375</v>
+        <v>-12.5</v>
       </c>
       <c r="E157" s="1">
         <v>1.11676E-5</v>
       </c>
       <c r="F157">
-        <v>-9.375</v>
+        <v>-12.5</v>
       </c>
       <c r="G157">
         <v>0</v>
       </c>
       <c r="H157">
-        <v>-10.9375</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A158">
-        <v>-9.4500000000000001E-3</v>
+        <v>-1.4120000000000001E-2</v>
       </c>
       <c r="B158">
-        <v>-7.8125</v>
+        <v>-10.9375</v>
       </c>
       <c r="C158">
-        <v>0</v>
+        <v>-1.0200000000000001E-3</v>
       </c>
       <c r="D158">
-        <v>-7.8125</v>
+        <v>-10.9375</v>
       </c>
       <c r="E158" s="1">
         <v>1.11676E-5</v>
       </c>
       <c r="F158">
-        <v>-7.8125</v>
+        <v>-10.9375</v>
       </c>
       <c r="G158">
         <v>0</v>
       </c>
       <c r="H158">
-        <v>-9.375</v>
+        <v>-10.9375</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A159">
-        <v>-5.9699999999999996E-3</v>
+        <v>-1.205E-2</v>
       </c>
       <c r="B159">
-        <v>-6.25</v>
-      </c>
-      <c r="C159">
-        <v>0</v>
+        <v>-9.375</v>
+      </c>
+      <c r="C159" s="1">
+        <v>-4.4670299999999998E-5</v>
       </c>
       <c r="D159">
-        <v>-6.25</v>
+        <v>-9.375</v>
       </c>
       <c r="E159" s="1">
         <v>1.11676E-5</v>
       </c>
       <c r="F159">
-        <v>-6.25</v>
+        <v>-9.375</v>
       </c>
       <c r="G159">
         <v>0</v>
       </c>
       <c r="H159">
-        <v>-7.8125</v>
+        <v>-9.375</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A160">
-        <v>-3.16E-3</v>
+        <v>-9.8799999999999999E-3</v>
       </c>
       <c r="B160">
-        <v>-4.6875</v>
-      </c>
-      <c r="C160">
-        <v>0</v>
+        <v>-7.8125</v>
+      </c>
+      <c r="C160" s="1">
+        <v>-1.11676E-5</v>
       </c>
       <c r="D160">
-        <v>-4.6875</v>
+        <v>-7.8125</v>
       </c>
       <c r="E160" s="1">
         <v>1.11676E-5</v>
       </c>
       <c r="F160">
-        <v>-4.6875</v>
+        <v>-7.8125</v>
       </c>
       <c r="G160">
         <v>0</v>
       </c>
       <c r="H160">
-        <v>-6.25</v>
+        <v>-7.8125</v>
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A161">
-        <v>-1.5100000000000001E-3</v>
+        <v>-7.43E-3</v>
       </c>
       <c r="B161">
-        <v>-3.125</v>
+        <v>-6.25</v>
       </c>
       <c r="C161" s="1">
-        <v>1.11676E-5</v>
+        <v>0</v>
       </c>
       <c r="D161">
-        <v>-3.125</v>
+        <v>-6.25</v>
       </c>
       <c r="E161" s="1">
         <v>1.11676E-5</v>
       </c>
       <c r="F161">
-        <v>-3.125</v>
+        <v>-6.25</v>
       </c>
       <c r="G161">
         <v>0</v>
       </c>
       <c r="H161">
-        <v>-4.6875</v>
+        <v>-6.25</v>
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A162" s="1">
-        <v>-5.3604399999999995E-4</v>
+        <v>-4.6600000000000001E-3</v>
       </c>
       <c r="B162">
-        <v>-1.5625</v>
+        <v>-4.6875</v>
       </c>
       <c r="C162" s="1">
         <v>1.11676E-5</v>
       </c>
       <c r="D162">
-        <v>-1.5625</v>
+        <v>-4.6875</v>
       </c>
       <c r="E162" s="1">
         <v>1.11676E-5</v>
       </c>
       <c r="F162">
-        <v>-1.5625</v>
+        <v>-4.6875</v>
       </c>
       <c r="G162">
         <v>0</v>
       </c>
       <c r="H162">
-        <v>-3.125</v>
+        <v>-4.6875</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A163">
-        <v>0</v>
+        <v>-2.2599999999999999E-3</v>
       </c>
       <c r="B163">
-        <v>0</v>
-      </c>
-      <c r="C163">
-        <v>0</v>
+        <v>-3.125</v>
+      </c>
+      <c r="C163" s="1">
+        <v>1.11676E-5</v>
       </c>
       <c r="D163">
-        <v>0</v>
-      </c>
-      <c r="E163">
-        <v>0</v>
+        <v>-3.125</v>
+      </c>
+      <c r="E163" s="1">
+        <v>1.11676E-5</v>
       </c>
       <c r="F163">
-        <v>0</v>
+        <v>-3.125</v>
       </c>
       <c r="G163">
         <v>0</v>
       </c>
       <c r="H163">
+        <v>-3.125</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A164" s="1">
+        <v>-7.2589300000000002E-4</v>
+      </c>
+      <c r="B164">
         <v>-1.5625</v>
       </c>
-    </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C164" s="1">
+        <v>1.11676E-5</v>
+      </c>
+      <c r="D164">
+        <v>-1.5625</v>
+      </c>
+      <c r="E164" s="1">
+        <v>1.11676E-5</v>
+      </c>
+      <c r="F164">
+        <v>-1.5625</v>
+      </c>
       <c r="G164">
         <v>0</v>
       </c>
       <c r="H164">
+        <v>-1.5625</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G165">
+        <v>0</v>
+      </c>
+      <c r="H165">
         <v>0</v>
       </c>
     </row>
